--- a/01_INPUTS/Stock/stock_VSB_Cuyo.xlsx
+++ b/01_INPUTS/Stock/stock_VSB_Cuyo.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25601"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC4CB4F7-42F4-4495-BB90-5749E6079018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7AD768F3-5EBD-4305-AFF7-9ADA04D26DEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10548" uniqueCount="711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10161" uniqueCount="711">
   <si>
     <t>Codigo</t>
   </si>
@@ -2231,8 +2231,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table1" displayName="Table1" ref="A1:L999">
-  <autoFilter ref="A1:L999" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table1" displayName="Table1" ref="A1:L956">
+  <autoFilter ref="A1:L956" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="CodigoReparto" totalsRowLabel="Total"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="CodigoItem"/>
@@ -3017,7 +3017,7 @@
         <v>456</v>
       </c>
       <c r="J8">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -3029,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -3073,7 +3073,7 @@
         <v>312</v>
       </c>
       <c r="J9">
-        <v>336</v>
+        <v>312</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -3085,7 +3085,7 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -3689,7 +3689,7 @@
         <v>1205</v>
       </c>
       <c r="J20">
-        <v>1217</v>
+        <v>1205</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="N20">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -3745,7 +3745,7 @@
         <v>2694</v>
       </c>
       <c r="J21">
-        <v>2730</v>
+        <v>2694</v>
       </c>
       <c r="K21">
         <v>0</v>
@@ -3757,7 +3757,7 @@
         <v>0</v>
       </c>
       <c r="N21">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -3801,7 +3801,7 @@
         <v>682</v>
       </c>
       <c r="J22">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -3813,7 +3813,7 @@
         <v>0</v>
       </c>
       <c r="N22">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -3969,7 +3969,7 @@
         <v>44</v>
       </c>
       <c r="J25">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -3981,7 +3981,7 @@
         <v>0</v>
       </c>
       <c r="N25">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O25">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>24</v>
       </c>
       <c r="I40">
-        <v>2218</v>
+        <v>1996</v>
       </c>
       <c r="J40">
         <v>2218</v>
@@ -4815,13 +4815,13 @@
         <v>0</v>
       </c>
       <c r="L40">
-        <v>2218</v>
+        <v>1996</v>
       </c>
       <c r="M40">
         <v>0</v>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="O40">
         <v>0</v>
@@ -4865,7 +4865,7 @@
         <v>1728</v>
       </c>
       <c r="J41">
-        <v>1740</v>
+        <v>1728</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -4877,7 +4877,7 @@
         <v>0</v>
       </c>
       <c r="N41">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -4918,22 +4918,22 @@
         <v>24</v>
       </c>
       <c r="I42">
+        <v>1884</v>
+      </c>
+      <c r="J42">
         <v>1896</v>
       </c>
-      <c r="J42">
-        <v>1914</v>
-      </c>
       <c r="K42">
         <v>0</v>
       </c>
       <c r="L42">
-        <v>1896</v>
+        <v>1884</v>
       </c>
       <c r="M42">
         <v>0</v>
       </c>
       <c r="N42">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="O42">
         <v>0</v>
@@ -4977,7 +4977,7 @@
         <v>240</v>
       </c>
       <c r="J43">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="K43">
         <v>0</v>
@@ -4989,7 +4989,7 @@
         <v>0</v>
       </c>
       <c r="N43">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O43">
         <v>0</v>
@@ -5982,7 +5982,7 @@
         <v>24</v>
       </c>
       <c r="I61">
-        <v>234</v>
+        <v>123</v>
       </c>
       <c r="J61">
         <v>234</v>
@@ -5991,13 +5991,13 @@
         <v>0</v>
       </c>
       <c r="L61">
-        <v>234</v>
+        <v>123</v>
       </c>
       <c r="M61">
         <v>0</v>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="O61">
         <v>0</v>
@@ -6206,7 +6206,7 @@
         <v>24</v>
       </c>
       <c r="I65">
-        <v>270</v>
+        <v>159</v>
       </c>
       <c r="J65">
         <v>270</v>
@@ -6215,13 +6215,13 @@
         <v>0</v>
       </c>
       <c r="L65">
-        <v>270</v>
+        <v>159</v>
       </c>
       <c r="M65">
         <v>0</v>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="O65">
         <v>0</v>
@@ -6545,7 +6545,7 @@
         <v>780</v>
       </c>
       <c r="J71">
-        <v>786</v>
+        <v>780</v>
       </c>
       <c r="K71">
         <v>0</v>
@@ -6557,7 +6557,7 @@
         <v>0</v>
       </c>
       <c r="N71">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -6654,22 +6654,22 @@
         <v>24</v>
       </c>
       <c r="I73">
+        <v>142</v>
+      </c>
+      <c r="J73">
         <v>253</v>
       </c>
-      <c r="J73">
-        <v>283</v>
-      </c>
       <c r="K73">
         <v>0</v>
       </c>
       <c r="L73">
-        <v>253</v>
+        <v>142</v>
       </c>
       <c r="M73">
         <v>0</v>
       </c>
       <c r="N73">
-        <v>30</v>
+        <v>111</v>
       </c>
       <c r="O73">
         <v>0</v>
@@ -7105,7 +7105,7 @@
         <v>229</v>
       </c>
       <c r="J81">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="K81">
         <v>0</v>
@@ -7117,7 +7117,7 @@
         <v>0</v>
       </c>
       <c r="N81">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O81">
         <v>0</v>
@@ -7273,7 +7273,7 @@
         <v>270</v>
       </c>
       <c r="J84">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="K84">
         <v>0</v>
@@ -7285,7 +7285,7 @@
         <v>0</v>
       </c>
       <c r="N84">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O84">
         <v>0</v>
@@ -7438,7 +7438,7 @@
         <v>24</v>
       </c>
       <c r="I87">
-        <v>624</v>
+        <v>513</v>
       </c>
       <c r="J87">
         <v>624</v>
@@ -7447,13 +7447,13 @@
         <v>0</v>
       </c>
       <c r="L87">
-        <v>624</v>
+        <v>513</v>
       </c>
       <c r="M87">
         <v>0</v>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="O87">
         <v>0</v>
@@ -7833,7 +7833,7 @@
         <v>213</v>
       </c>
       <c r="J94">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="K94">
         <v>0</v>
@@ -7845,7 +7845,7 @@
         <v>0</v>
       </c>
       <c r="N94">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>24</v>
       </c>
       <c r="I113">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="J113">
         <v>261</v>
@@ -8903,13 +8903,13 @@
         <v>0</v>
       </c>
       <c r="L113">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="M113">
         <v>0</v>
       </c>
       <c r="N113">
-        <v>150</v>
+        <v>261</v>
       </c>
       <c r="O113">
         <v>0</v>
@@ -9793,7 +9793,7 @@
         <v>12</v>
       </c>
       <c r="J129">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K129">
         <v>0</v>
@@ -9805,7 +9805,7 @@
         <v>0</v>
       </c>
       <c r="N129">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O129">
         <v>0</v>
@@ -10571,7 +10571,7 @@
         <v>72</v>
       </c>
       <c r="J143">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="K143">
         <v>0</v>
@@ -10583,7 +10583,7 @@
         <v>0</v>
       </c>
       <c r="N143">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O143">
         <v>0</v>
@@ -11187,7 +11187,7 @@
         <v>648</v>
       </c>
       <c r="J154">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="K154">
         <v>0</v>
@@ -11199,7 +11199,7 @@
         <v>0</v>
       </c>
       <c r="N154">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O154">
         <v>0</v>
@@ -12195,7 +12195,7 @@
         <v>186</v>
       </c>
       <c r="J172">
-        <v>222</v>
+        <v>186</v>
       </c>
       <c r="K172">
         <v>0</v>
@@ -12207,7 +12207,7 @@
         <v>0</v>
       </c>
       <c r="N172">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="O172">
         <v>0</v>
@@ -12233,7 +12233,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L999"/>
+  <dimension ref="A1:L956"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -44321,16 +44321,16 @@
     </row>
     <row r="845" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A845">
-        <v>4601</v>
+        <v>4603</v>
       </c>
       <c r="B845" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C845" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D845" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="E845" t="s">
         <v>374</v>
@@ -44348,27 +44348,27 @@
         <v>24</v>
       </c>
       <c r="J845">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="K845">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="L845" t="s">
-        <v>403</v>
+        <v>25</v>
       </c>
     </row>
     <row r="846" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A846">
-        <v>4601</v>
+        <v>4603</v>
       </c>
       <c r="B846" t="s">
-        <v>598</v>
+        <v>399</v>
       </c>
       <c r="C846" t="s">
-        <v>599</v>
+        <v>400</v>
       </c>
       <c r="D846" t="s">
-        <v>598</v>
+        <v>399</v>
       </c>
       <c r="E846" t="s">
         <v>374</v>
@@ -44386,27 +44386,27 @@
         <v>24</v>
       </c>
       <c r="J846">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="K846">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L846" t="s">
-        <v>539</v>
+        <v>25</v>
       </c>
     </row>
     <row r="847" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A847">
-        <v>4601</v>
+        <v>4603</v>
       </c>
       <c r="B847" t="s">
-        <v>422</v>
+        <v>311</v>
       </c>
       <c r="C847" t="s">
-        <v>423</v>
+        <v>312</v>
       </c>
       <c r="D847" t="s">
-        <v>422</v>
+        <v>311</v>
       </c>
       <c r="E847" t="s">
         <v>374</v>
@@ -44424,27 +44424,27 @@
         <v>24</v>
       </c>
       <c r="J847">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K847">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L847" t="s">
-        <v>424</v>
+        <v>25</v>
       </c>
     </row>
     <row r="848" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A848">
-        <v>4601</v>
+        <v>4603</v>
       </c>
       <c r="B848" t="s">
-        <v>428</v>
+        <v>534</v>
       </c>
       <c r="C848" t="s">
-        <v>429</v>
+        <v>535</v>
       </c>
       <c r="D848" t="s">
-        <v>428</v>
+        <v>534</v>
       </c>
       <c r="E848" t="s">
         <v>374</v>
@@ -44465,24 +44465,24 @@
         <v>0</v>
       </c>
       <c r="K848">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L848" t="s">
-        <v>427</v>
+        <v>536</v>
       </c>
     </row>
     <row r="849" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A849">
-        <v>4601</v>
+        <v>4603</v>
       </c>
       <c r="B849" t="s">
-        <v>436</v>
+        <v>595</v>
       </c>
       <c r="C849" t="s">
-        <v>437</v>
+        <v>596</v>
       </c>
       <c r="D849" t="s">
-        <v>436</v>
+        <v>595</v>
       </c>
       <c r="E849" t="s">
         <v>374</v>
@@ -44503,24 +44503,24 @@
         <v>0</v>
       </c>
       <c r="K849">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L849" t="s">
-        <v>435</v>
+        <v>597</v>
       </c>
     </row>
     <row r="850" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A850">
-        <v>4601</v>
+        <v>4603</v>
       </c>
       <c r="B850" t="s">
-        <v>438</v>
+        <v>401</v>
       </c>
       <c r="C850" t="s">
-        <v>439</v>
+        <v>402</v>
       </c>
       <c r="D850" t="s">
-        <v>438</v>
+        <v>401</v>
       </c>
       <c r="E850" t="s">
         <v>374</v>
@@ -44541,24 +44541,24 @@
         <v>0</v>
       </c>
       <c r="K850">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L850" t="s">
-        <v>440</v>
+        <v>403</v>
       </c>
     </row>
     <row r="851" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A851">
-        <v>4601</v>
+        <v>4603</v>
       </c>
       <c r="B851" t="s">
-        <v>441</v>
+        <v>404</v>
       </c>
       <c r="C851" t="s">
-        <v>442</v>
+        <v>405</v>
       </c>
       <c r="D851" t="s">
-        <v>441</v>
+        <v>404</v>
       </c>
       <c r="E851" t="s">
         <v>374</v>
@@ -44579,24 +44579,24 @@
         <v>0</v>
       </c>
       <c r="K851">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L851" t="s">
-        <v>443</v>
+        <v>406</v>
       </c>
     </row>
     <row r="852" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A852">
-        <v>4601</v>
+        <v>4603</v>
       </c>
       <c r="B852" t="s">
-        <v>444</v>
+        <v>626</v>
       </c>
       <c r="C852" t="s">
-        <v>445</v>
+        <v>627</v>
       </c>
       <c r="D852" t="s">
-        <v>444</v>
+        <v>626</v>
       </c>
       <c r="E852" t="s">
         <v>374</v>
@@ -44617,24 +44617,24 @@
         <v>0</v>
       </c>
       <c r="K852">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L852" t="s">
-        <v>446</v>
+        <v>539</v>
       </c>
     </row>
     <row r="853" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A853">
-        <v>4601</v>
+        <v>4603</v>
       </c>
       <c r="B853" t="s">
-        <v>452</v>
+        <v>598</v>
       </c>
       <c r="C853" t="s">
-        <v>453</v>
+        <v>599</v>
       </c>
       <c r="D853" t="s">
-        <v>452</v>
+        <v>598</v>
       </c>
       <c r="E853" t="s">
         <v>374</v>
@@ -44655,24 +44655,24 @@
         <v>0</v>
       </c>
       <c r="K853">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="L853" t="s">
-        <v>454</v>
+        <v>539</v>
       </c>
     </row>
     <row r="854" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A854">
-        <v>4601</v>
+        <v>4603</v>
       </c>
       <c r="B854" t="s">
-        <v>468</v>
+        <v>413</v>
       </c>
       <c r="C854" t="s">
-        <v>469</v>
+        <v>414</v>
       </c>
       <c r="D854" t="s">
-        <v>468</v>
+        <v>413</v>
       </c>
       <c r="E854" t="s">
         <v>374</v>
@@ -44693,24 +44693,24 @@
         <v>0</v>
       </c>
       <c r="K854">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L854" t="s">
-        <v>470</v>
+        <v>415</v>
       </c>
     </row>
     <row r="855" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A855">
-        <v>4601</v>
+        <v>4603</v>
       </c>
       <c r="B855" t="s">
-        <v>476</v>
+        <v>600</v>
       </c>
       <c r="C855" t="s">
-        <v>477</v>
+        <v>601</v>
       </c>
       <c r="D855" t="s">
-        <v>476</v>
+        <v>600</v>
       </c>
       <c r="E855" t="s">
         <v>374</v>
@@ -44728,27 +44728,27 @@
         <v>24</v>
       </c>
       <c r="J855">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K855">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="L855" t="s">
-        <v>478</v>
+        <v>539</v>
       </c>
     </row>
     <row r="856" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A856">
-        <v>4601</v>
+        <v>4603</v>
       </c>
       <c r="B856" t="s">
-        <v>492</v>
+        <v>416</v>
       </c>
       <c r="C856" t="s">
-        <v>493</v>
+        <v>417</v>
       </c>
       <c r="D856" t="s">
-        <v>492</v>
+        <v>416</v>
       </c>
       <c r="E856" t="s">
         <v>374</v>
@@ -44769,24 +44769,24 @@
         <v>0</v>
       </c>
       <c r="K856">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L856" t="s">
-        <v>443</v>
+        <v>418</v>
       </c>
     </row>
     <row r="857" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A857">
-        <v>4601</v>
+        <v>4603</v>
       </c>
       <c r="B857" t="s">
-        <v>494</v>
+        <v>658</v>
       </c>
       <c r="C857" t="s">
-        <v>495</v>
+        <v>659</v>
       </c>
       <c r="D857" t="s">
-        <v>494</v>
+        <v>658</v>
       </c>
       <c r="E857" t="s">
         <v>374</v>
@@ -44807,24 +44807,24 @@
         <v>0</v>
       </c>
       <c r="K857">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L857" t="s">
-        <v>421</v>
+        <v>536</v>
       </c>
     </row>
     <row r="858" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A858">
-        <v>4601</v>
+        <v>4603</v>
       </c>
       <c r="B858" t="s">
-        <v>496</v>
+        <v>604</v>
       </c>
       <c r="C858" t="s">
-        <v>497</v>
+        <v>605</v>
       </c>
       <c r="D858" t="s">
-        <v>496</v>
+        <v>604</v>
       </c>
       <c r="E858" t="s">
         <v>374</v>
@@ -44848,21 +44848,21 @@
         <v>3</v>
       </c>
       <c r="L858" t="s">
-        <v>443</v>
+        <v>606</v>
       </c>
     </row>
     <row r="859" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A859">
-        <v>4601</v>
+        <v>4603</v>
       </c>
       <c r="B859" t="s">
-        <v>547</v>
+        <v>607</v>
       </c>
       <c r="C859" t="s">
-        <v>548</v>
+        <v>608</v>
       </c>
       <c r="D859" t="s">
-        <v>547</v>
+        <v>607</v>
       </c>
       <c r="E859" t="s">
         <v>374</v>
@@ -44883,24 +44883,24 @@
         <v>0</v>
       </c>
       <c r="K859">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="L859" t="s">
-        <v>440</v>
+        <v>606</v>
       </c>
     </row>
     <row r="860" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A860">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B860" t="s">
-        <v>397</v>
+        <v>422</v>
       </c>
       <c r="C860" t="s">
-        <v>398</v>
+        <v>423</v>
       </c>
       <c r="D860" t="s">
-        <v>397</v>
+        <v>422</v>
       </c>
       <c r="E860" t="s">
         <v>374</v>
@@ -44918,27 +44918,27 @@
         <v>24</v>
       </c>
       <c r="J860">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K860">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L860" t="s">
-        <v>25</v>
+        <v>424</v>
       </c>
     </row>
     <row r="861" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A861">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B861" t="s">
-        <v>401</v>
+        <v>425</v>
       </c>
       <c r="C861" t="s">
-        <v>402</v>
+        <v>426</v>
       </c>
       <c r="D861" t="s">
-        <v>401</v>
+        <v>425</v>
       </c>
       <c r="E861" t="s">
         <v>374</v>
@@ -44956,27 +44956,27 @@
         <v>24</v>
       </c>
       <c r="J861">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K861">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="L861" t="s">
-        <v>403</v>
+        <v>427</v>
       </c>
     </row>
     <row r="862" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A862">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B862" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="C862" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="D862" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="E862" t="s">
         <v>374</v>
@@ -44997,24 +44997,24 @@
         <v>0</v>
       </c>
       <c r="K862">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="L862" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
     </row>
     <row r="863" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A863">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B863" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="C863" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="D863" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="E863" t="s">
         <v>374</v>
@@ -45035,24 +45035,24 @@
         <v>0</v>
       </c>
       <c r="K863">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L863" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
     </row>
     <row r="864" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A864">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B864" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="C864" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="D864" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="E864" t="s">
         <v>374</v>
@@ -45073,24 +45073,24 @@
         <v>0</v>
       </c>
       <c r="K864">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L864" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
     </row>
     <row r="865" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A865">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B865" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="C865" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="D865" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="E865" t="s">
         <v>374</v>
@@ -45108,27 +45108,27 @@
         <v>24</v>
       </c>
       <c r="J865">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K865">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L865" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
     </row>
     <row r="866" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A866">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B866" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C866" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D866" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E866" t="s">
         <v>374</v>
@@ -45146,18 +45146,18 @@
         <v>24</v>
       </c>
       <c r="J866">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K866">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="L866" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="867" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A867">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B867" t="s">
         <v>441</v>
@@ -45184,10 +45184,10 @@
         <v>24</v>
       </c>
       <c r="J867">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K867">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L867" t="s">
         <v>443</v>
@@ -45195,7 +45195,7 @@
     </row>
     <row r="868" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A868">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B868" t="s">
         <v>444</v>
@@ -45222,10 +45222,10 @@
         <v>24</v>
       </c>
       <c r="J868">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K868">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="L868" t="s">
         <v>446</v>
@@ -45233,7 +45233,7 @@
     </row>
     <row r="869" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A869">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B869" t="s">
         <v>447</v>
@@ -45263,7 +45263,7 @@
         <v>1</v>
       </c>
       <c r="K869">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L869" t="s">
         <v>449</v>
@@ -45271,16 +45271,16 @@
     </row>
     <row r="870" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A870">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B870" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C870" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D870" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E870" t="s">
         <v>374</v>
@@ -45298,27 +45298,27 @@
         <v>24</v>
       </c>
       <c r="J870">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K870">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="L870" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
     </row>
     <row r="871" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A871">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B871" t="s">
-        <v>468</v>
+        <v>542</v>
       </c>
       <c r="C871" t="s">
-        <v>469</v>
+        <v>543</v>
       </c>
       <c r="D871" t="s">
-        <v>468</v>
+        <v>542</v>
       </c>
       <c r="E871" t="s">
         <v>374</v>
@@ -45339,24 +45339,24 @@
         <v>0</v>
       </c>
       <c r="K871">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L871" t="s">
-        <v>470</v>
+        <v>544</v>
       </c>
     </row>
     <row r="872" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A872">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B872" t="s">
-        <v>611</v>
+        <v>452</v>
       </c>
       <c r="C872" t="s">
-        <v>612</v>
+        <v>453</v>
       </c>
       <c r="D872" t="s">
-        <v>611</v>
+        <v>452</v>
       </c>
       <c r="E872" t="s">
         <v>374</v>
@@ -45377,24 +45377,24 @@
         <v>0</v>
       </c>
       <c r="K872">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="L872" t="s">
-        <v>487</v>
+        <v>454</v>
       </c>
     </row>
     <row r="873" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A873">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B873" t="s">
-        <v>476</v>
+        <v>455</v>
       </c>
       <c r="C873" t="s">
-        <v>477</v>
+        <v>456</v>
       </c>
       <c r="D873" t="s">
-        <v>476</v>
+        <v>455</v>
       </c>
       <c r="E873" t="s">
         <v>374</v>
@@ -45412,27 +45412,27 @@
         <v>24</v>
       </c>
       <c r="J873">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K873">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L873" t="s">
-        <v>478</v>
+        <v>457</v>
       </c>
     </row>
     <row r="874" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A874">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B874" t="s">
-        <v>492</v>
+        <v>458</v>
       </c>
       <c r="C874" t="s">
-        <v>493</v>
+        <v>459</v>
       </c>
       <c r="D874" t="s">
-        <v>492</v>
+        <v>458</v>
       </c>
       <c r="E874" t="s">
         <v>374</v>
@@ -45453,24 +45453,24 @@
         <v>0</v>
       </c>
       <c r="K874">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L874" t="s">
-        <v>443</v>
+        <v>457</v>
       </c>
     </row>
     <row r="875" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A875">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B875" t="s">
-        <v>494</v>
+        <v>460</v>
       </c>
       <c r="C875" t="s">
-        <v>495</v>
+        <v>461</v>
       </c>
       <c r="D875" t="s">
-        <v>494</v>
+        <v>460</v>
       </c>
       <c r="E875" t="s">
         <v>374</v>
@@ -45491,24 +45491,24 @@
         <v>0</v>
       </c>
       <c r="K875">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L875" t="s">
-        <v>421</v>
+        <v>462</v>
       </c>
     </row>
     <row r="876" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A876">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B876" t="s">
-        <v>496</v>
+        <v>463</v>
       </c>
       <c r="C876" t="s">
-        <v>497</v>
+        <v>464</v>
       </c>
       <c r="D876" t="s">
-        <v>496</v>
+        <v>463</v>
       </c>
       <c r="E876" t="s">
         <v>374</v>
@@ -45529,24 +45529,24 @@
         <v>0</v>
       </c>
       <c r="K876">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="L876" t="s">
-        <v>443</v>
+        <v>462</v>
       </c>
     </row>
     <row r="877" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A877">
-        <v>4602</v>
+        <v>4603</v>
       </c>
       <c r="B877" t="s">
-        <v>547</v>
+        <v>468</v>
       </c>
       <c r="C877" t="s">
-        <v>548</v>
+        <v>469</v>
       </c>
       <c r="D877" t="s">
-        <v>547</v>
+        <v>468</v>
       </c>
       <c r="E877" t="s">
         <v>374</v>
@@ -45564,13 +45564,13 @@
         <v>24</v>
       </c>
       <c r="J877">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K877">
         <v>10</v>
       </c>
       <c r="L877" t="s">
-        <v>440</v>
+        <v>470</v>
       </c>
     </row>
     <row r="878" spans="1:12" x14ac:dyDescent="0.25">
@@ -45578,13 +45578,13 @@
         <v>4603</v>
       </c>
       <c r="B878" t="s">
-        <v>397</v>
+        <v>611</v>
       </c>
       <c r="C878" t="s">
-        <v>398</v>
+        <v>612</v>
       </c>
       <c r="D878" t="s">
-        <v>397</v>
+        <v>611</v>
       </c>
       <c r="E878" t="s">
         <v>374</v>
@@ -45602,13 +45602,13 @@
         <v>24</v>
       </c>
       <c r="J878">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="K878">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="L878" t="s">
-        <v>25</v>
+        <v>487</v>
       </c>
     </row>
     <row r="879" spans="1:12" x14ac:dyDescent="0.25">
@@ -45616,13 +45616,13 @@
         <v>4603</v>
       </c>
       <c r="B879" t="s">
-        <v>399</v>
+        <v>471</v>
       </c>
       <c r="C879" t="s">
-        <v>400</v>
+        <v>472</v>
       </c>
       <c r="D879" t="s">
-        <v>399</v>
+        <v>471</v>
       </c>
       <c r="E879" t="s">
         <v>374</v>
@@ -45640,13 +45640,13 @@
         <v>24</v>
       </c>
       <c r="J879">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="K879">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L879" t="s">
-        <v>25</v>
+        <v>473</v>
       </c>
     </row>
     <row r="880" spans="1:12" x14ac:dyDescent="0.25">
@@ -45654,13 +45654,13 @@
         <v>4603</v>
       </c>
       <c r="B880" t="s">
-        <v>311</v>
+        <v>476</v>
       </c>
       <c r="C880" t="s">
-        <v>312</v>
+        <v>477</v>
       </c>
       <c r="D880" t="s">
-        <v>311</v>
+        <v>476</v>
       </c>
       <c r="E880" t="s">
         <v>374</v>
@@ -45678,13 +45678,13 @@
         <v>24</v>
       </c>
       <c r="J880">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K880">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L880" t="s">
-        <v>25</v>
+        <v>478</v>
       </c>
     </row>
     <row r="881" spans="1:12" x14ac:dyDescent="0.25">
@@ -45692,13 +45692,13 @@
         <v>4603</v>
       </c>
       <c r="B881" t="s">
-        <v>534</v>
+        <v>667</v>
       </c>
       <c r="C881" t="s">
-        <v>535</v>
+        <v>668</v>
       </c>
       <c r="D881" t="s">
-        <v>534</v>
+        <v>667</v>
       </c>
       <c r="E881" t="s">
         <v>374</v>
@@ -45719,10 +45719,10 @@
         <v>0</v>
       </c>
       <c r="K881">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="L881" t="s">
-        <v>536</v>
+        <v>443</v>
       </c>
     </row>
     <row r="882" spans="1:12" x14ac:dyDescent="0.25">
@@ -45730,13 +45730,13 @@
         <v>4603</v>
       </c>
       <c r="B882" t="s">
-        <v>595</v>
+        <v>545</v>
       </c>
       <c r="C882" t="s">
-        <v>596</v>
+        <v>546</v>
       </c>
       <c r="D882" t="s">
-        <v>595</v>
+        <v>545</v>
       </c>
       <c r="E882" t="s">
         <v>374</v>
@@ -45760,7 +45760,7 @@
         <v>5</v>
       </c>
       <c r="L882" t="s">
-        <v>597</v>
+        <v>443</v>
       </c>
     </row>
     <row r="883" spans="1:12" x14ac:dyDescent="0.25">
@@ -45768,13 +45768,13 @@
         <v>4603</v>
       </c>
       <c r="B883" t="s">
-        <v>401</v>
+        <v>483</v>
       </c>
       <c r="C883" t="s">
-        <v>402</v>
+        <v>484</v>
       </c>
       <c r="D883" t="s">
-        <v>401</v>
+        <v>483</v>
       </c>
       <c r="E883" t="s">
         <v>374</v>
@@ -45795,10 +45795,10 @@
         <v>0</v>
       </c>
       <c r="K883">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L883" t="s">
-        <v>403</v>
+        <v>470</v>
       </c>
     </row>
     <row r="884" spans="1:12" x14ac:dyDescent="0.25">
@@ -45806,13 +45806,13 @@
         <v>4603</v>
       </c>
       <c r="B884" t="s">
-        <v>404</v>
+        <v>488</v>
       </c>
       <c r="C884" t="s">
-        <v>405</v>
+        <v>489</v>
       </c>
       <c r="D884" t="s">
-        <v>404</v>
+        <v>488</v>
       </c>
       <c r="E884" t="s">
         <v>374</v>
@@ -45833,10 +45833,10 @@
         <v>0</v>
       </c>
       <c r="K884">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L884" t="s">
-        <v>406</v>
+        <v>443</v>
       </c>
     </row>
     <row r="885" spans="1:12" x14ac:dyDescent="0.25">
@@ -45844,13 +45844,13 @@
         <v>4603</v>
       </c>
       <c r="B885" t="s">
-        <v>626</v>
+        <v>490</v>
       </c>
       <c r="C885" t="s">
-        <v>627</v>
+        <v>491</v>
       </c>
       <c r="D885" t="s">
-        <v>626</v>
+        <v>490</v>
       </c>
       <c r="E885" t="s">
         <v>374</v>
@@ -45871,10 +45871,10 @@
         <v>0</v>
       </c>
       <c r="K885">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L885" t="s">
-        <v>539</v>
+        <v>443</v>
       </c>
     </row>
     <row r="886" spans="1:12" x14ac:dyDescent="0.25">
@@ -45882,13 +45882,13 @@
         <v>4603</v>
       </c>
       <c r="B886" t="s">
-        <v>598</v>
+        <v>492</v>
       </c>
       <c r="C886" t="s">
-        <v>599</v>
+        <v>493</v>
       </c>
       <c r="D886" t="s">
-        <v>598</v>
+        <v>492</v>
       </c>
       <c r="E886" t="s">
         <v>374</v>
@@ -45909,10 +45909,10 @@
         <v>0</v>
       </c>
       <c r="K886">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="L886" t="s">
-        <v>539</v>
+        <v>443</v>
       </c>
     </row>
     <row r="887" spans="1:12" x14ac:dyDescent="0.25">
@@ -45920,13 +45920,13 @@
         <v>4603</v>
       </c>
       <c r="B887" t="s">
-        <v>413</v>
+        <v>494</v>
       </c>
       <c r="C887" t="s">
-        <v>414</v>
+        <v>495</v>
       </c>
       <c r="D887" t="s">
-        <v>413</v>
+        <v>494</v>
       </c>
       <c r="E887" t="s">
         <v>374</v>
@@ -45947,10 +45947,10 @@
         <v>0</v>
       </c>
       <c r="K887">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="L887" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="888" spans="1:12" x14ac:dyDescent="0.25">
@@ -45958,13 +45958,13 @@
         <v>4603</v>
       </c>
       <c r="B888" t="s">
-        <v>600</v>
+        <v>702</v>
       </c>
       <c r="C888" t="s">
-        <v>601</v>
+        <v>703</v>
       </c>
       <c r="D888" t="s">
-        <v>600</v>
+        <v>702</v>
       </c>
       <c r="E888" t="s">
         <v>374</v>
@@ -45985,10 +45985,10 @@
         <v>0</v>
       </c>
       <c r="K888">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L888" t="s">
-        <v>539</v>
+        <v>704</v>
       </c>
     </row>
     <row r="889" spans="1:12" x14ac:dyDescent="0.25">
@@ -45996,13 +45996,13 @@
         <v>4603</v>
       </c>
       <c r="B889" t="s">
-        <v>416</v>
+        <v>496</v>
       </c>
       <c r="C889" t="s">
-        <v>417</v>
+        <v>497</v>
       </c>
       <c r="D889" t="s">
-        <v>416</v>
+        <v>496</v>
       </c>
       <c r="E889" t="s">
         <v>374</v>
@@ -46023,10 +46023,10 @@
         <v>0</v>
       </c>
       <c r="K889">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="L889" t="s">
-        <v>418</v>
+        <v>443</v>
       </c>
     </row>
     <row r="890" spans="1:12" x14ac:dyDescent="0.25">
@@ -46034,13 +46034,13 @@
         <v>4603</v>
       </c>
       <c r="B890" t="s">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="C890" t="s">
-        <v>659</v>
+        <v>511</v>
       </c>
       <c r="D890" t="s">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="E890" t="s">
         <v>374</v>
@@ -46064,7 +46064,7 @@
         <v>3</v>
       </c>
       <c r="L890" t="s">
-        <v>536</v>
+        <v>409</v>
       </c>
     </row>
     <row r="891" spans="1:12" x14ac:dyDescent="0.25">
@@ -46072,13 +46072,13 @@
         <v>4603</v>
       </c>
       <c r="B891" t="s">
-        <v>604</v>
+        <v>613</v>
       </c>
       <c r="C891" t="s">
-        <v>605</v>
+        <v>614</v>
       </c>
       <c r="D891" t="s">
-        <v>604</v>
+        <v>613</v>
       </c>
       <c r="E891" t="s">
         <v>374</v>
@@ -46099,10 +46099,10 @@
         <v>0</v>
       </c>
       <c r="K891">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L891" t="s">
-        <v>606</v>
+        <v>449</v>
       </c>
     </row>
     <row r="892" spans="1:12" x14ac:dyDescent="0.25">
@@ -46110,13 +46110,13 @@
         <v>4603</v>
       </c>
       <c r="B892" t="s">
-        <v>607</v>
+        <v>547</v>
       </c>
       <c r="C892" t="s">
-        <v>608</v>
+        <v>548</v>
       </c>
       <c r="D892" t="s">
-        <v>607</v>
+        <v>547</v>
       </c>
       <c r="E892" t="s">
         <v>374</v>
@@ -46137,10 +46137,10 @@
         <v>0</v>
       </c>
       <c r="K892">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="L892" t="s">
-        <v>606</v>
+        <v>440</v>
       </c>
     </row>
     <row r="893" spans="1:12" x14ac:dyDescent="0.25">
@@ -46148,13 +46148,13 @@
         <v>4603</v>
       </c>
       <c r="B893" t="s">
-        <v>422</v>
+        <v>512</v>
       </c>
       <c r="C893" t="s">
-        <v>423</v>
+        <v>513</v>
       </c>
       <c r="D893" t="s">
-        <v>422</v>
+        <v>512</v>
       </c>
       <c r="E893" t="s">
         <v>374</v>
@@ -46175,10 +46175,10 @@
         <v>0</v>
       </c>
       <c r="K893">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L893" t="s">
-        <v>424</v>
+        <v>454</v>
       </c>
     </row>
     <row r="894" spans="1:12" x14ac:dyDescent="0.25">
@@ -46186,13 +46186,13 @@
         <v>4603</v>
       </c>
       <c r="B894" t="s">
-        <v>425</v>
+        <v>549</v>
       </c>
       <c r="C894" t="s">
-        <v>426</v>
+        <v>550</v>
       </c>
       <c r="D894" t="s">
-        <v>425</v>
+        <v>549</v>
       </c>
       <c r="E894" t="s">
         <v>374</v>
@@ -46213,10 +46213,10 @@
         <v>0</v>
       </c>
       <c r="K894">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="L894" t="s">
-        <v>427</v>
+        <v>551</v>
       </c>
     </row>
     <row r="895" spans="1:12" x14ac:dyDescent="0.25">
@@ -46224,13 +46224,13 @@
         <v>4603</v>
       </c>
       <c r="B895" t="s">
-        <v>428</v>
+        <v>523</v>
       </c>
       <c r="C895" t="s">
-        <v>429</v>
+        <v>524</v>
       </c>
       <c r="D895" t="s">
-        <v>428</v>
+        <v>523</v>
       </c>
       <c r="E895" t="s">
         <v>374</v>
@@ -46251,10 +46251,10 @@
         <v>0</v>
       </c>
       <c r="K895">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="L895" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
     </row>
     <row r="896" spans="1:12" x14ac:dyDescent="0.25">
@@ -46262,13 +46262,13 @@
         <v>4603</v>
       </c>
       <c r="B896" t="s">
-        <v>430</v>
+        <v>525</v>
       </c>
       <c r="C896" t="s">
-        <v>431</v>
+        <v>526</v>
       </c>
       <c r="D896" t="s">
-        <v>430</v>
+        <v>525</v>
       </c>
       <c r="E896" t="s">
         <v>374</v>
@@ -46289,10 +46289,10 @@
         <v>0</v>
       </c>
       <c r="K896">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L896" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
     </row>
     <row r="897" spans="1:12" x14ac:dyDescent="0.25">
@@ -46300,13 +46300,13 @@
         <v>4603</v>
       </c>
       <c r="B897" t="s">
-        <v>433</v>
+        <v>60</v>
       </c>
       <c r="C897" t="s">
-        <v>434</v>
+        <v>61</v>
       </c>
       <c r="D897" t="s">
-        <v>433</v>
+        <v>60</v>
       </c>
       <c r="E897" t="s">
         <v>374</v>
@@ -46324,13 +46324,13 @@
         <v>24</v>
       </c>
       <c r="J897">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="K897">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L897" t="s">
-        <v>435</v>
+        <v>25</v>
       </c>
     </row>
     <row r="898" spans="1:12" x14ac:dyDescent="0.25">
@@ -46338,13 +46338,13 @@
         <v>4603</v>
       </c>
       <c r="B898" t="s">
-        <v>436</v>
+        <v>62</v>
       </c>
       <c r="C898" t="s">
-        <v>437</v>
+        <v>63</v>
       </c>
       <c r="D898" t="s">
-        <v>436</v>
+        <v>62</v>
       </c>
       <c r="E898" t="s">
         <v>374</v>
@@ -46362,13 +46362,13 @@
         <v>24</v>
       </c>
       <c r="J898">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="K898">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L898" t="s">
-        <v>435</v>
+        <v>25</v>
       </c>
     </row>
     <row r="899" spans="1:12" x14ac:dyDescent="0.25">
@@ -46376,13 +46376,13 @@
         <v>4603</v>
       </c>
       <c r="B899" t="s">
-        <v>438</v>
+        <v>84</v>
       </c>
       <c r="C899" t="s">
-        <v>439</v>
+        <v>85</v>
       </c>
       <c r="D899" t="s">
-        <v>438</v>
+        <v>84</v>
       </c>
       <c r="E899" t="s">
         <v>374</v>
@@ -46400,13 +46400,13 @@
         <v>24</v>
       </c>
       <c r="J899">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K899">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L899" t="s">
-        <v>440</v>
+        <v>25</v>
       </c>
     </row>
     <row r="900" spans="1:12" x14ac:dyDescent="0.25">
@@ -46414,13 +46414,13 @@
         <v>4603</v>
       </c>
       <c r="B900" t="s">
-        <v>441</v>
+        <v>276</v>
       </c>
       <c r="C900" t="s">
-        <v>442</v>
+        <v>277</v>
       </c>
       <c r="D900" t="s">
-        <v>441</v>
+        <v>276</v>
       </c>
       <c r="E900" t="s">
         <v>374</v>
@@ -46438,13 +46438,13 @@
         <v>24</v>
       </c>
       <c r="J900">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K900">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L900" t="s">
-        <v>443</v>
+        <v>25</v>
       </c>
     </row>
     <row r="901" spans="1:12" x14ac:dyDescent="0.25">
@@ -46452,13 +46452,13 @@
         <v>4603</v>
       </c>
       <c r="B901" t="s">
-        <v>444</v>
+        <v>110</v>
       </c>
       <c r="C901" t="s">
-        <v>445</v>
+        <v>111</v>
       </c>
       <c r="D901" t="s">
-        <v>444</v>
+        <v>110</v>
       </c>
       <c r="E901" t="s">
         <v>374</v>
@@ -46476,13 +46476,13 @@
         <v>24</v>
       </c>
       <c r="J901">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="K901">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L901" t="s">
-        <v>446</v>
+        <v>25</v>
       </c>
     </row>
     <row r="902" spans="1:12" x14ac:dyDescent="0.25">
@@ -46490,13 +46490,13 @@
         <v>4603</v>
       </c>
       <c r="B902" t="s">
-        <v>447</v>
+        <v>150</v>
       </c>
       <c r="C902" t="s">
-        <v>448</v>
+        <v>151</v>
       </c>
       <c r="D902" t="s">
-        <v>447</v>
+        <v>150</v>
       </c>
       <c r="E902" t="s">
         <v>374</v>
@@ -46514,13 +46514,13 @@
         <v>24</v>
       </c>
       <c r="J902">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="K902">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L902" t="s">
-        <v>449</v>
+        <v>25</v>
       </c>
     </row>
     <row r="903" spans="1:12" x14ac:dyDescent="0.25">
@@ -46528,13 +46528,13 @@
         <v>4603</v>
       </c>
       <c r="B903" t="s">
-        <v>450</v>
+        <v>162</v>
       </c>
       <c r="C903" t="s">
-        <v>451</v>
+        <v>163</v>
       </c>
       <c r="D903" t="s">
-        <v>450</v>
+        <v>162</v>
       </c>
       <c r="E903" t="s">
         <v>374</v>
@@ -46552,13 +46552,13 @@
         <v>24</v>
       </c>
       <c r="J903">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K903">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L903" t="s">
-        <v>449</v>
+        <v>25</v>
       </c>
     </row>
     <row r="904" spans="1:12" x14ac:dyDescent="0.25">
@@ -46566,13 +46566,13 @@
         <v>4603</v>
       </c>
       <c r="B904" t="s">
-        <v>542</v>
+        <v>164</v>
       </c>
       <c r="C904" t="s">
-        <v>543</v>
+        <v>165</v>
       </c>
       <c r="D904" t="s">
-        <v>542</v>
+        <v>164</v>
       </c>
       <c r="E904" t="s">
         <v>374</v>
@@ -46590,13 +46590,13 @@
         <v>24</v>
       </c>
       <c r="J904">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K904">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L904" t="s">
-        <v>544</v>
+        <v>25</v>
       </c>
     </row>
     <row r="905" spans="1:12" x14ac:dyDescent="0.25">
@@ -46604,13 +46604,13 @@
         <v>4603</v>
       </c>
       <c r="B905" t="s">
-        <v>452</v>
+        <v>634</v>
       </c>
       <c r="C905" t="s">
-        <v>453</v>
+        <v>635</v>
       </c>
       <c r="D905" t="s">
-        <v>452</v>
+        <v>634</v>
       </c>
       <c r="E905" t="s">
         <v>374</v>
@@ -46628,13 +46628,13 @@
         <v>24</v>
       </c>
       <c r="J905">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K905">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L905" t="s">
-        <v>454</v>
+        <v>25</v>
       </c>
     </row>
     <row r="906" spans="1:12" x14ac:dyDescent="0.25">
@@ -46642,13 +46642,13 @@
         <v>4603</v>
       </c>
       <c r="B906" t="s">
-        <v>455</v>
+        <v>206</v>
       </c>
       <c r="C906" t="s">
-        <v>456</v>
+        <v>207</v>
       </c>
       <c r="D906" t="s">
-        <v>455</v>
+        <v>206</v>
       </c>
       <c r="E906" t="s">
         <v>374</v>
@@ -46666,13 +46666,13 @@
         <v>24</v>
       </c>
       <c r="J906">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K906">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L906" t="s">
-        <v>457</v>
+        <v>25</v>
       </c>
     </row>
     <row r="907" spans="1:12" x14ac:dyDescent="0.25">
@@ -46680,13 +46680,13 @@
         <v>4603</v>
       </c>
       <c r="B907" t="s">
-        <v>458</v>
+        <v>220</v>
       </c>
       <c r="C907" t="s">
-        <v>459</v>
+        <v>221</v>
       </c>
       <c r="D907" t="s">
-        <v>458</v>
+        <v>220</v>
       </c>
       <c r="E907" t="s">
         <v>374</v>
@@ -46704,13 +46704,13 @@
         <v>24</v>
       </c>
       <c r="J907">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K907">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L907" t="s">
-        <v>457</v>
+        <v>25</v>
       </c>
     </row>
     <row r="908" spans="1:12" x14ac:dyDescent="0.25">
@@ -46718,13 +46718,13 @@
         <v>4603</v>
       </c>
       <c r="B908" t="s">
-        <v>460</v>
+        <v>234</v>
       </c>
       <c r="C908" t="s">
-        <v>461</v>
+        <v>235</v>
       </c>
       <c r="D908" t="s">
-        <v>460</v>
+        <v>234</v>
       </c>
       <c r="E908" t="s">
         <v>374</v>
@@ -46742,13 +46742,13 @@
         <v>24</v>
       </c>
       <c r="J908">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K908">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L908" t="s">
-        <v>462</v>
+        <v>25</v>
       </c>
     </row>
     <row r="909" spans="1:12" x14ac:dyDescent="0.25">
@@ -46756,13 +46756,13 @@
         <v>4603</v>
       </c>
       <c r="B909" t="s">
-        <v>463</v>
+        <v>272</v>
       </c>
       <c r="C909" t="s">
-        <v>464</v>
+        <v>273</v>
       </c>
       <c r="D909" t="s">
-        <v>463</v>
+        <v>272</v>
       </c>
       <c r="E909" t="s">
         <v>374</v>
@@ -46780,13 +46780,13 @@
         <v>24</v>
       </c>
       <c r="J909">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K909">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L909" t="s">
-        <v>462</v>
+        <v>25</v>
       </c>
     </row>
     <row r="910" spans="1:12" x14ac:dyDescent="0.25">
@@ -46794,13 +46794,13 @@
         <v>4603</v>
       </c>
       <c r="B910" t="s">
-        <v>468</v>
+        <v>242</v>
       </c>
       <c r="C910" t="s">
-        <v>469</v>
+        <v>243</v>
       </c>
       <c r="D910" t="s">
-        <v>468</v>
+        <v>242</v>
       </c>
       <c r="E910" t="s">
         <v>374</v>
@@ -46818,13 +46818,13 @@
         <v>24</v>
       </c>
       <c r="J910">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K910">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L910" t="s">
-        <v>470</v>
+        <v>25</v>
       </c>
     </row>
     <row r="911" spans="1:12" x14ac:dyDescent="0.25">
@@ -46832,13 +46832,13 @@
         <v>4603</v>
       </c>
       <c r="B911" t="s">
-        <v>611</v>
+        <v>246</v>
       </c>
       <c r="C911" t="s">
-        <v>612</v>
+        <v>247</v>
       </c>
       <c r="D911" t="s">
-        <v>611</v>
+        <v>246</v>
       </c>
       <c r="E911" t="s">
         <v>374</v>
@@ -46856,27 +46856,27 @@
         <v>24</v>
       </c>
       <c r="J911">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K911">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="L911" t="s">
-        <v>487</v>
+        <v>25</v>
       </c>
     </row>
     <row r="912" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A912">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B912" t="s">
-        <v>471</v>
+        <v>36</v>
       </c>
       <c r="C912" t="s">
-        <v>472</v>
+        <v>37</v>
       </c>
       <c r="D912" t="s">
-        <v>471</v>
+        <v>36</v>
       </c>
       <c r="E912" t="s">
         <v>374</v>
@@ -46894,27 +46894,27 @@
         <v>24</v>
       </c>
       <c r="J912">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K912">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L912" t="s">
-        <v>473</v>
+        <v>25</v>
       </c>
     </row>
     <row r="913" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A913">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B913" t="s">
-        <v>476</v>
+        <v>311</v>
       </c>
       <c r="C913" t="s">
-        <v>477</v>
+        <v>312</v>
       </c>
       <c r="D913" t="s">
-        <v>476</v>
+        <v>311</v>
       </c>
       <c r="E913" t="s">
         <v>374</v>
@@ -46932,27 +46932,27 @@
         <v>24</v>
       </c>
       <c r="J913">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K913">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L913" t="s">
-        <v>478</v>
+        <v>25</v>
       </c>
     </row>
     <row r="914" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A914">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B914" t="s">
-        <v>667</v>
+        <v>48</v>
       </c>
       <c r="C914" t="s">
-        <v>668</v>
+        <v>49</v>
       </c>
       <c r="D914" t="s">
-        <v>667</v>
+        <v>48</v>
       </c>
       <c r="E914" t="s">
         <v>374</v>
@@ -46970,27 +46970,27 @@
         <v>24</v>
       </c>
       <c r="J914">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K914">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L914" t="s">
-        <v>443</v>
+        <v>25</v>
       </c>
     </row>
     <row r="915" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A915">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B915" t="s">
-        <v>545</v>
+        <v>54</v>
       </c>
       <c r="C915" t="s">
-        <v>546</v>
+        <v>55</v>
       </c>
       <c r="D915" t="s">
-        <v>545</v>
+        <v>54</v>
       </c>
       <c r="E915" t="s">
         <v>374</v>
@@ -47008,27 +47008,27 @@
         <v>24</v>
       </c>
       <c r="J915">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K915">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L915" t="s">
-        <v>443</v>
+        <v>25</v>
       </c>
     </row>
     <row r="916" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A916">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B916" t="s">
-        <v>483</v>
+        <v>444</v>
       </c>
       <c r="C916" t="s">
-        <v>484</v>
+        <v>445</v>
       </c>
       <c r="D916" t="s">
-        <v>483</v>
+        <v>444</v>
       </c>
       <c r="E916" t="s">
         <v>374</v>
@@ -47049,24 +47049,24 @@
         <v>0</v>
       </c>
       <c r="K916">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L916" t="s">
-        <v>470</v>
+        <v>446</v>
       </c>
     </row>
     <row r="917" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A917">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B917" t="s">
-        <v>488</v>
+        <v>455</v>
       </c>
       <c r="C917" t="s">
-        <v>489</v>
+        <v>456</v>
       </c>
       <c r="D917" t="s">
-        <v>488</v>
+        <v>455</v>
       </c>
       <c r="E917" t="s">
         <v>374</v>
@@ -47087,24 +47087,24 @@
         <v>0</v>
       </c>
       <c r="K917">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L917" t="s">
-        <v>443</v>
+        <v>457</v>
       </c>
     </row>
     <row r="918" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A918">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B918" t="s">
-        <v>490</v>
+        <v>458</v>
       </c>
       <c r="C918" t="s">
-        <v>491</v>
+        <v>459</v>
       </c>
       <c r="D918" t="s">
-        <v>490</v>
+        <v>458</v>
       </c>
       <c r="E918" t="s">
         <v>374</v>
@@ -47125,24 +47125,24 @@
         <v>0</v>
       </c>
       <c r="K918">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L918" t="s">
-        <v>443</v>
+        <v>457</v>
       </c>
     </row>
     <row r="919" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A919">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B919" t="s">
-        <v>492</v>
+        <v>460</v>
       </c>
       <c r="C919" t="s">
-        <v>493</v>
+        <v>461</v>
       </c>
       <c r="D919" t="s">
-        <v>492</v>
+        <v>460</v>
       </c>
       <c r="E919" t="s">
         <v>374</v>
@@ -47163,24 +47163,24 @@
         <v>0</v>
       </c>
       <c r="K919">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L919" t="s">
-        <v>443</v>
+        <v>462</v>
       </c>
     </row>
     <row r="920" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A920">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B920" t="s">
-        <v>494</v>
+        <v>463</v>
       </c>
       <c r="C920" t="s">
-        <v>495</v>
+        <v>464</v>
       </c>
       <c r="D920" t="s">
-        <v>494</v>
+        <v>463</v>
       </c>
       <c r="E920" t="s">
         <v>374</v>
@@ -47201,24 +47201,24 @@
         <v>0</v>
       </c>
       <c r="K920">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="L920" t="s">
-        <v>421</v>
+        <v>462</v>
       </c>
     </row>
     <row r="921" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A921">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B921" t="s">
-        <v>702</v>
+        <v>667</v>
       </c>
       <c r="C921" t="s">
-        <v>703</v>
+        <v>668</v>
       </c>
       <c r="D921" t="s">
-        <v>702</v>
+        <v>667</v>
       </c>
       <c r="E921" t="s">
         <v>374</v>
@@ -47239,24 +47239,24 @@
         <v>0</v>
       </c>
       <c r="K921">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L921" t="s">
-        <v>704</v>
+        <v>443</v>
       </c>
     </row>
     <row r="922" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A922">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B922" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="C922" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="D922" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="E922" t="s">
         <v>374</v>
@@ -47277,7 +47277,7 @@
         <v>0</v>
       </c>
       <c r="K922">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L922" t="s">
         <v>443</v>
@@ -47285,16 +47285,16 @@
     </row>
     <row r="923" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A923">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B923" t="s">
-        <v>510</v>
+        <v>490</v>
       </c>
       <c r="C923" t="s">
-        <v>511</v>
+        <v>491</v>
       </c>
       <c r="D923" t="s">
-        <v>510</v>
+        <v>490</v>
       </c>
       <c r="E923" t="s">
         <v>374</v>
@@ -47315,24 +47315,24 @@
         <v>0</v>
       </c>
       <c r="K923">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L923" t="s">
-        <v>409</v>
+        <v>443</v>
       </c>
     </row>
     <row r="924" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A924">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B924" t="s">
-        <v>613</v>
+        <v>492</v>
       </c>
       <c r="C924" t="s">
-        <v>614</v>
+        <v>493</v>
       </c>
       <c r="D924" t="s">
-        <v>613</v>
+        <v>492</v>
       </c>
       <c r="E924" t="s">
         <v>374</v>
@@ -47356,21 +47356,21 @@
         <v>8</v>
       </c>
       <c r="L924" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
     </row>
     <row r="925" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A925">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B925" t="s">
-        <v>547</v>
+        <v>514</v>
       </c>
       <c r="C925" t="s">
-        <v>548</v>
+        <v>515</v>
       </c>
       <c r="D925" t="s">
-        <v>547</v>
+        <v>514</v>
       </c>
       <c r="E925" t="s">
         <v>374</v>
@@ -47391,24 +47391,24 @@
         <v>0</v>
       </c>
       <c r="K925">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L925" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="926" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A926">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B926" t="s">
-        <v>512</v>
+        <v>58</v>
       </c>
       <c r="C926" t="s">
-        <v>513</v>
+        <v>59</v>
       </c>
       <c r="D926" t="s">
-        <v>512</v>
+        <v>58</v>
       </c>
       <c r="E926" t="s">
         <v>374</v>
@@ -47426,27 +47426,27 @@
         <v>24</v>
       </c>
       <c r="J926">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K926">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L926" t="s">
-        <v>454</v>
+        <v>25</v>
       </c>
     </row>
     <row r="927" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A927">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B927" t="s">
-        <v>549</v>
+        <v>60</v>
       </c>
       <c r="C927" t="s">
-        <v>550</v>
+        <v>61</v>
       </c>
       <c r="D927" t="s">
-        <v>549</v>
+        <v>60</v>
       </c>
       <c r="E927" t="s">
         <v>374</v>
@@ -47464,27 +47464,27 @@
         <v>24</v>
       </c>
       <c r="J927">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="K927">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L927" t="s">
-        <v>551</v>
+        <v>25</v>
       </c>
     </row>
     <row r="928" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A928">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B928" t="s">
-        <v>523</v>
+        <v>62</v>
       </c>
       <c r="C928" t="s">
-        <v>524</v>
+        <v>63</v>
       </c>
       <c r="D928" t="s">
-        <v>523</v>
+        <v>62</v>
       </c>
       <c r="E928" t="s">
         <v>374</v>
@@ -47502,27 +47502,27 @@
         <v>24</v>
       </c>
       <c r="J928">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="K928">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L928" t="s">
-        <v>435</v>
+        <v>25</v>
       </c>
     </row>
     <row r="929" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A929">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B929" t="s">
-        <v>525</v>
+        <v>68</v>
       </c>
       <c r="C929" t="s">
-        <v>526</v>
+        <v>69</v>
       </c>
       <c r="D929" t="s">
-        <v>525</v>
+        <v>68</v>
       </c>
       <c r="E929" t="s">
         <v>374</v>
@@ -47540,27 +47540,27 @@
         <v>24</v>
       </c>
       <c r="J929">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K929">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L929" t="s">
-        <v>440</v>
+        <v>25</v>
       </c>
     </row>
     <row r="930" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A930">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B930" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="C930" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="D930" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="E930" t="s">
         <v>374</v>
@@ -47578,7 +47578,7 @@
         <v>24</v>
       </c>
       <c r="J930">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="K930">
         <v>0</v>
@@ -47589,16 +47589,16 @@
     </row>
     <row r="931" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A931">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B931" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="C931" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="D931" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="E931" t="s">
         <v>374</v>
@@ -47616,7 +47616,7 @@
         <v>24</v>
       </c>
       <c r="J931">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="K931">
         <v>0</v>
@@ -47627,16 +47627,16 @@
     </row>
     <row r="932" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A932">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B932" t="s">
-        <v>84</v>
+        <v>280</v>
       </c>
       <c r="C932" t="s">
-        <v>85</v>
+        <v>281</v>
       </c>
       <c r="D932" t="s">
-        <v>84</v>
+        <v>280</v>
       </c>
       <c r="E932" t="s">
         <v>374</v>
@@ -47654,7 +47654,7 @@
         <v>24</v>
       </c>
       <c r="J932">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K932">
         <v>0</v>
@@ -47665,16 +47665,16 @@
     </row>
     <row r="933" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A933">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B933" t="s">
-        <v>276</v>
+        <v>705</v>
       </c>
       <c r="C933" t="s">
-        <v>277</v>
+        <v>706</v>
       </c>
       <c r="D933" t="s">
-        <v>276</v>
+        <v>705</v>
       </c>
       <c r="E933" t="s">
         <v>374</v>
@@ -47692,7 +47692,7 @@
         <v>24</v>
       </c>
       <c r="J933">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K933">
         <v>0</v>
@@ -47703,16 +47703,16 @@
     </row>
     <row r="934" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A934">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B934" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="C934" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="D934" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="E934" t="s">
         <v>374</v>
@@ -47741,16 +47741,16 @@
     </row>
     <row r="935" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A935">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B935" t="s">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="C935" t="s">
-        <v>151</v>
+        <v>101</v>
       </c>
       <c r="D935" t="s">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="E935" t="s">
         <v>374</v>
@@ -47768,7 +47768,7 @@
         <v>24</v>
       </c>
       <c r="J935">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="K935">
         <v>0</v>
@@ -47779,16 +47779,16 @@
     </row>
     <row r="936" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A936">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B936" t="s">
-        <v>162</v>
+        <v>104</v>
       </c>
       <c r="C936" t="s">
-        <v>163</v>
+        <v>105</v>
       </c>
       <c r="D936" t="s">
-        <v>162</v>
+        <v>104</v>
       </c>
       <c r="E936" t="s">
         <v>374</v>
@@ -47806,7 +47806,7 @@
         <v>24</v>
       </c>
       <c r="J936">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="K936">
         <v>0</v>
@@ -47817,16 +47817,16 @@
     </row>
     <row r="937" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A937">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B937" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="C937" t="s">
-        <v>165</v>
+        <v>111</v>
       </c>
       <c r="D937" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E937" t="s">
         <v>374</v>
@@ -47855,16 +47855,16 @@
     </row>
     <row r="938" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A938">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B938" t="s">
-        <v>634</v>
+        <v>124</v>
       </c>
       <c r="C938" t="s">
-        <v>635</v>
+        <v>125</v>
       </c>
       <c r="D938" t="s">
-        <v>634</v>
+        <v>124</v>
       </c>
       <c r="E938" t="s">
         <v>374</v>
@@ -47893,16 +47893,16 @@
     </row>
     <row r="939" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A939">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B939" t="s">
-        <v>206</v>
+        <v>134</v>
       </c>
       <c r="C939" t="s">
-        <v>207</v>
+        <v>135</v>
       </c>
       <c r="D939" t="s">
-        <v>206</v>
+        <v>134</v>
       </c>
       <c r="E939" t="s">
         <v>374</v>
@@ -47920,7 +47920,7 @@
         <v>24</v>
       </c>
       <c r="J939">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K939">
         <v>0</v>
@@ -47931,16 +47931,16 @@
     </row>
     <row r="940" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A940">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B940" t="s">
-        <v>220</v>
+        <v>144</v>
       </c>
       <c r="C940" t="s">
-        <v>221</v>
+        <v>145</v>
       </c>
       <c r="D940" t="s">
-        <v>220</v>
+        <v>144</v>
       </c>
       <c r="E940" t="s">
         <v>374</v>
@@ -47958,7 +47958,7 @@
         <v>24</v>
       </c>
       <c r="J940">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="K940">
         <v>0</v>
@@ -47969,16 +47969,16 @@
     </row>
     <row r="941" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A941">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B941" t="s">
-        <v>234</v>
+        <v>150</v>
       </c>
       <c r="C941" t="s">
-        <v>235</v>
+        <v>151</v>
       </c>
       <c r="D941" t="s">
-        <v>234</v>
+        <v>150</v>
       </c>
       <c r="E941" t="s">
         <v>374</v>
@@ -47996,7 +47996,7 @@
         <v>24</v>
       </c>
       <c r="J941">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="K941">
         <v>0</v>
@@ -48007,16 +48007,16 @@
     </row>
     <row r="942" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A942">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B942" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C942" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D942" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E942" t="s">
         <v>374</v>
@@ -48034,7 +48034,7 @@
         <v>24</v>
       </c>
       <c r="J942">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K942">
         <v>0</v>
@@ -48045,16 +48045,16 @@
     </row>
     <row r="943" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A943">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B943" t="s">
-        <v>242</v>
+        <v>554</v>
       </c>
       <c r="C943" t="s">
-        <v>243</v>
+        <v>555</v>
       </c>
       <c r="D943" t="s">
-        <v>242</v>
+        <v>554</v>
       </c>
       <c r="E943" t="s">
         <v>374</v>
@@ -48072,7 +48072,7 @@
         <v>24</v>
       </c>
       <c r="J943">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K943">
         <v>0</v>
@@ -48083,16 +48083,16 @@
     </row>
     <row r="944" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A944">
-        <v>4603</v>
+        <v>4604</v>
       </c>
       <c r="B944" t="s">
-        <v>246</v>
+        <v>162</v>
       </c>
       <c r="C944" t="s">
-        <v>247</v>
+        <v>163</v>
       </c>
       <c r="D944" t="s">
-        <v>246</v>
+        <v>162</v>
       </c>
       <c r="E944" t="s">
         <v>374</v>
@@ -48110,7 +48110,7 @@
         <v>24</v>
       </c>
       <c r="J944">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="K944">
         <v>0</v>
@@ -48124,13 +48124,13 @@
         <v>4604</v>
       </c>
       <c r="B945" t="s">
-        <v>36</v>
+        <v>172</v>
       </c>
       <c r="C945" t="s">
-        <v>37</v>
+        <v>173</v>
       </c>
       <c r="D945" t="s">
-        <v>36</v>
+        <v>172</v>
       </c>
       <c r="E945" t="s">
         <v>374</v>
@@ -48148,7 +48148,7 @@
         <v>24</v>
       </c>
       <c r="J945">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K945">
         <v>0</v>
@@ -48162,13 +48162,13 @@
         <v>4604</v>
       </c>
       <c r="B946" t="s">
-        <v>311</v>
+        <v>634</v>
       </c>
       <c r="C946" t="s">
-        <v>312</v>
+        <v>635</v>
       </c>
       <c r="D946" t="s">
-        <v>311</v>
+        <v>634</v>
       </c>
       <c r="E946" t="s">
         <v>374</v>
@@ -48186,7 +48186,7 @@
         <v>24</v>
       </c>
       <c r="J946">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K946">
         <v>0</v>
@@ -48200,13 +48200,13 @@
         <v>4604</v>
       </c>
       <c r="B947" t="s">
-        <v>48</v>
+        <v>206</v>
       </c>
       <c r="C947" t="s">
-        <v>49</v>
+        <v>207</v>
       </c>
       <c r="D947" t="s">
-        <v>48</v>
+        <v>206</v>
       </c>
       <c r="E947" t="s">
         <v>374</v>
@@ -48224,7 +48224,7 @@
         <v>24</v>
       </c>
       <c r="J947">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="K947">
         <v>0</v>
@@ -48238,13 +48238,13 @@
         <v>4604</v>
       </c>
       <c r="B948" t="s">
-        <v>54</v>
+        <v>208</v>
       </c>
       <c r="C948" t="s">
-        <v>55</v>
+        <v>209</v>
       </c>
       <c r="D948" t="s">
-        <v>54</v>
+        <v>208</v>
       </c>
       <c r="E948" t="s">
         <v>374</v>
@@ -48262,7 +48262,7 @@
         <v>24</v>
       </c>
       <c r="J948">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K948">
         <v>0</v>
@@ -48276,13 +48276,13 @@
         <v>4604</v>
       </c>
       <c r="B949" t="s">
-        <v>444</v>
+        <v>210</v>
       </c>
       <c r="C949" t="s">
-        <v>445</v>
+        <v>211</v>
       </c>
       <c r="D949" t="s">
-        <v>444</v>
+        <v>210</v>
       </c>
       <c r="E949" t="s">
         <v>374</v>
@@ -48300,13 +48300,13 @@
         <v>24</v>
       </c>
       <c r="J949">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K949">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L949" t="s">
-        <v>446</v>
+        <v>25</v>
       </c>
     </row>
     <row r="950" spans="1:12" x14ac:dyDescent="0.25">
@@ -48314,13 +48314,13 @@
         <v>4604</v>
       </c>
       <c r="B950" t="s">
-        <v>455</v>
+        <v>220</v>
       </c>
       <c r="C950" t="s">
-        <v>456</v>
+        <v>221</v>
       </c>
       <c r="D950" t="s">
-        <v>455</v>
+        <v>220</v>
       </c>
       <c r="E950" t="s">
         <v>374</v>
@@ -48338,13 +48338,13 @@
         <v>24</v>
       </c>
       <c r="J950">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K950">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L950" t="s">
-        <v>457</v>
+        <v>25</v>
       </c>
     </row>
     <row r="951" spans="1:12" x14ac:dyDescent="0.25">
@@ -48352,13 +48352,13 @@
         <v>4604</v>
       </c>
       <c r="B951" t="s">
-        <v>458</v>
+        <v>707</v>
       </c>
       <c r="C951" t="s">
-        <v>459</v>
+        <v>708</v>
       </c>
       <c r="D951" t="s">
-        <v>458</v>
+        <v>707</v>
       </c>
       <c r="E951" t="s">
         <v>374</v>
@@ -48376,13 +48376,13 @@
         <v>24</v>
       </c>
       <c r="J951">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K951">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L951" t="s">
-        <v>457</v>
+        <v>25</v>
       </c>
     </row>
     <row r="952" spans="1:12" x14ac:dyDescent="0.25">
@@ -48390,13 +48390,13 @@
         <v>4604</v>
       </c>
       <c r="B952" t="s">
-        <v>460</v>
+        <v>697</v>
       </c>
       <c r="C952" t="s">
-        <v>461</v>
+        <v>698</v>
       </c>
       <c r="D952" t="s">
-        <v>460</v>
+        <v>697</v>
       </c>
       <c r="E952" t="s">
         <v>374</v>
@@ -48414,13 +48414,13 @@
         <v>24</v>
       </c>
       <c r="J952">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K952">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L952" t="s">
-        <v>462</v>
+        <v>25</v>
       </c>
     </row>
     <row r="953" spans="1:12" x14ac:dyDescent="0.25">
@@ -48428,13 +48428,13 @@
         <v>4604</v>
       </c>
       <c r="B953" t="s">
-        <v>463</v>
+        <v>709</v>
       </c>
       <c r="C953" t="s">
-        <v>464</v>
+        <v>710</v>
       </c>
       <c r="D953" t="s">
-        <v>463</v>
+        <v>709</v>
       </c>
       <c r="E953" t="s">
         <v>374</v>
@@ -48452,13 +48452,13 @@
         <v>24</v>
       </c>
       <c r="J953">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K953">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L953" t="s">
-        <v>462</v>
+        <v>25</v>
       </c>
     </row>
     <row r="954" spans="1:12" x14ac:dyDescent="0.25">
@@ -48466,13 +48466,13 @@
         <v>4604</v>
       </c>
       <c r="B954" t="s">
-        <v>667</v>
+        <v>292</v>
       </c>
       <c r="C954" t="s">
-        <v>668</v>
+        <v>293</v>
       </c>
       <c r="D954" t="s">
-        <v>667</v>
+        <v>292</v>
       </c>
       <c r="E954" t="s">
         <v>374</v>
@@ -48490,13 +48490,13 @@
         <v>24</v>
       </c>
       <c r="J954">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K954">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L954" t="s">
-        <v>443</v>
+        <v>25</v>
       </c>
     </row>
     <row r="955" spans="1:12" x14ac:dyDescent="0.25">
@@ -48504,13 +48504,13 @@
         <v>4604</v>
       </c>
       <c r="B955" t="s">
-        <v>488</v>
+        <v>244</v>
       </c>
       <c r="C955" t="s">
-        <v>489</v>
+        <v>245</v>
       </c>
       <c r="D955" t="s">
-        <v>488</v>
+        <v>244</v>
       </c>
       <c r="E955" t="s">
         <v>374</v>
@@ -48528,13 +48528,13 @@
         <v>24</v>
       </c>
       <c r="J955">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K955">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L955" t="s">
-        <v>443</v>
+        <v>25</v>
       </c>
     </row>
     <row r="956" spans="1:12" x14ac:dyDescent="0.25">
@@ -48542,13 +48542,13 @@
         <v>4604</v>
       </c>
       <c r="B956" t="s">
-        <v>490</v>
+        <v>266</v>
       </c>
       <c r="C956" t="s">
-        <v>491</v>
+        <v>267</v>
       </c>
       <c r="D956" t="s">
-        <v>490</v>
+        <v>266</v>
       </c>
       <c r="E956" t="s">
         <v>374</v>
@@ -48566,1647 +48566,13 @@
         <v>24</v>
       </c>
       <c r="J956">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K956">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L956" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="957" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A957">
-        <v>4604</v>
-      </c>
-      <c r="B957" t="s">
-        <v>492</v>
-      </c>
-      <c r="C957" t="s">
-        <v>493</v>
-      </c>
-      <c r="D957" t="s">
-        <v>492</v>
-      </c>
-      <c r="E957" t="s">
-        <v>374</v>
-      </c>
-      <c r="F957" t="s">
-        <v>24</v>
-      </c>
-      <c r="G957" t="s">
-        <v>375</v>
-      </c>
-      <c r="H957" t="s">
-        <v>376</v>
-      </c>
-      <c r="I957" t="s">
-        <v>24</v>
-      </c>
-      <c r="J957">
-        <v>0</v>
-      </c>
-      <c r="K957">
-        <v>8</v>
-      </c>
-      <c r="L957" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="958" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A958">
-        <v>4604</v>
-      </c>
-      <c r="B958" t="s">
-        <v>514</v>
-      </c>
-      <c r="C958" t="s">
-        <v>515</v>
-      </c>
-      <c r="D958" t="s">
-        <v>514</v>
-      </c>
-      <c r="E958" t="s">
-        <v>374</v>
-      </c>
-      <c r="F958" t="s">
-        <v>24</v>
-      </c>
-      <c r="G958" t="s">
-        <v>375</v>
-      </c>
-      <c r="H958" t="s">
-        <v>376</v>
-      </c>
-      <c r="I958" t="s">
-        <v>24</v>
-      </c>
-      <c r="J958">
-        <v>0</v>
-      </c>
-      <c r="K958">
-        <v>8</v>
-      </c>
-      <c r="L958" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="959" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A959">
-        <v>4604</v>
-      </c>
-      <c r="B959" t="s">
-        <v>58</v>
-      </c>
-      <c r="C959" t="s">
-        <v>59</v>
-      </c>
-      <c r="D959" t="s">
-        <v>58</v>
-      </c>
-      <c r="E959" t="s">
-        <v>374</v>
-      </c>
-      <c r="F959" t="s">
-        <v>24</v>
-      </c>
-      <c r="G959" t="s">
-        <v>375</v>
-      </c>
-      <c r="H959" t="s">
-        <v>376</v>
-      </c>
-      <c r="I959" t="s">
-        <v>24</v>
-      </c>
-      <c r="J959">
-        <v>12</v>
-      </c>
-      <c r="K959">
-        <v>0</v>
-      </c>
-      <c r="L959" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="960" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A960">
-        <v>4604</v>
-      </c>
-      <c r="B960" t="s">
-        <v>60</v>
-      </c>
-      <c r="C960" t="s">
-        <v>61</v>
-      </c>
-      <c r="D960" t="s">
-        <v>60</v>
-      </c>
-      <c r="E960" t="s">
-        <v>374</v>
-      </c>
-      <c r="F960" t="s">
-        <v>24</v>
-      </c>
-      <c r="G960" t="s">
-        <v>375</v>
-      </c>
-      <c r="H960" t="s">
-        <v>376</v>
-      </c>
-      <c r="I960" t="s">
-        <v>24</v>
-      </c>
-      <c r="J960">
-        <v>42</v>
-      </c>
-      <c r="K960">
-        <v>0</v>
-      </c>
-      <c r="L960" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="961" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A961">
-        <v>4604</v>
-      </c>
-      <c r="B961" t="s">
-        <v>62</v>
-      </c>
-      <c r="C961" t="s">
-        <v>63</v>
-      </c>
-      <c r="D961" t="s">
-        <v>62</v>
-      </c>
-      <c r="E961" t="s">
-        <v>374</v>
-      </c>
-      <c r="F961" t="s">
-        <v>24</v>
-      </c>
-      <c r="G961" t="s">
-        <v>375</v>
-      </c>
-      <c r="H961" t="s">
-        <v>376</v>
-      </c>
-      <c r="I961" t="s">
-        <v>24</v>
-      </c>
-      <c r="J961">
-        <v>186</v>
-      </c>
-      <c r="K961">
-        <v>0</v>
-      </c>
-      <c r="L961" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="962" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A962">
-        <v>4604</v>
-      </c>
-      <c r="B962" t="s">
-        <v>68</v>
-      </c>
-      <c r="C962" t="s">
-        <v>69</v>
-      </c>
-      <c r="D962" t="s">
-        <v>68</v>
-      </c>
-      <c r="E962" t="s">
-        <v>374</v>
-      </c>
-      <c r="F962" t="s">
-        <v>24</v>
-      </c>
-      <c r="G962" t="s">
-        <v>375</v>
-      </c>
-      <c r="H962" t="s">
-        <v>376</v>
-      </c>
-      <c r="I962" t="s">
-        <v>24</v>
-      </c>
-      <c r="J962">
-        <v>12</v>
-      </c>
-      <c r="K962">
-        <v>0</v>
-      </c>
-      <c r="L962" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="963" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A963">
-        <v>4604</v>
-      </c>
-      <c r="B963" t="s">
-        <v>82</v>
-      </c>
-      <c r="C963" t="s">
-        <v>83</v>
-      </c>
-      <c r="D963" t="s">
-        <v>82</v>
-      </c>
-      <c r="E963" t="s">
-        <v>374</v>
-      </c>
-      <c r="F963" t="s">
-        <v>24</v>
-      </c>
-      <c r="G963" t="s">
-        <v>375</v>
-      </c>
-      <c r="H963" t="s">
-        <v>376</v>
-      </c>
-      <c r="I963" t="s">
-        <v>24</v>
-      </c>
-      <c r="J963">
-        <v>2</v>
-      </c>
-      <c r="K963">
-        <v>0</v>
-      </c>
-      <c r="L963" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="964" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A964">
-        <v>4604</v>
-      </c>
-      <c r="B964" t="s">
-        <v>84</v>
-      </c>
-      <c r="C964" t="s">
-        <v>85</v>
-      </c>
-      <c r="D964" t="s">
-        <v>84</v>
-      </c>
-      <c r="E964" t="s">
-        <v>374</v>
-      </c>
-      <c r="F964" t="s">
-        <v>24</v>
-      </c>
-      <c r="G964" t="s">
-        <v>375</v>
-      </c>
-      <c r="H964" t="s">
-        <v>376</v>
-      </c>
-      <c r="I964" t="s">
-        <v>24</v>
-      </c>
-      <c r="J964">
-        <v>90</v>
-      </c>
-      <c r="K964">
-        <v>0</v>
-      </c>
-      <c r="L964" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="965" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A965">
-        <v>4604</v>
-      </c>
-      <c r="B965" t="s">
-        <v>280</v>
-      </c>
-      <c r="C965" t="s">
-        <v>281</v>
-      </c>
-      <c r="D965" t="s">
-        <v>280</v>
-      </c>
-      <c r="E965" t="s">
-        <v>374</v>
-      </c>
-      <c r="F965" t="s">
-        <v>24</v>
-      </c>
-      <c r="G965" t="s">
-        <v>375</v>
-      </c>
-      <c r="H965" t="s">
-        <v>376</v>
-      </c>
-      <c r="I965" t="s">
-        <v>24</v>
-      </c>
-      <c r="J965">
-        <v>6</v>
-      </c>
-      <c r="K965">
-        <v>0</v>
-      </c>
-      <c r="L965" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="966" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A966">
-        <v>4604</v>
-      </c>
-      <c r="B966" t="s">
-        <v>705</v>
-      </c>
-      <c r="C966" t="s">
-        <v>706</v>
-      </c>
-      <c r="D966" t="s">
-        <v>705</v>
-      </c>
-      <c r="E966" t="s">
-        <v>374</v>
-      </c>
-      <c r="F966" t="s">
-        <v>24</v>
-      </c>
-      <c r="G966" t="s">
-        <v>375</v>
-      </c>
-      <c r="H966" t="s">
-        <v>376</v>
-      </c>
-      <c r="I966" t="s">
-        <v>24</v>
-      </c>
-      <c r="J966">
-        <v>1</v>
-      </c>
-      <c r="K966">
-        <v>0</v>
-      </c>
-      <c r="L966" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="967" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A967">
-        <v>4604</v>
-      </c>
-      <c r="B967" t="s">
-        <v>94</v>
-      </c>
-      <c r="C967" t="s">
-        <v>95</v>
-      </c>
-      <c r="D967" t="s">
-        <v>94</v>
-      </c>
-      <c r="E967" t="s">
-        <v>374</v>
-      </c>
-      <c r="F967" t="s">
-        <v>24</v>
-      </c>
-      <c r="G967" t="s">
-        <v>375</v>
-      </c>
-      <c r="H967" t="s">
-        <v>376</v>
-      </c>
-      <c r="I967" t="s">
-        <v>24</v>
-      </c>
-      <c r="J967">
-        <v>24</v>
-      </c>
-      <c r="K967">
-        <v>0</v>
-      </c>
-      <c r="L967" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="968" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A968">
-        <v>4604</v>
-      </c>
-      <c r="B968" t="s">
-        <v>100</v>
-      </c>
-      <c r="C968" t="s">
-        <v>101</v>
-      </c>
-      <c r="D968" t="s">
-        <v>100</v>
-      </c>
-      <c r="E968" t="s">
-        <v>374</v>
-      </c>
-      <c r="F968" t="s">
-        <v>24</v>
-      </c>
-      <c r="G968" t="s">
-        <v>375</v>
-      </c>
-      <c r="H968" t="s">
-        <v>376</v>
-      </c>
-      <c r="I968" t="s">
-        <v>24</v>
-      </c>
-      <c r="J968">
-        <v>6</v>
-      </c>
-      <c r="K968">
-        <v>0</v>
-      </c>
-      <c r="L968" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="969" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A969">
-        <v>4604</v>
-      </c>
-      <c r="B969" t="s">
-        <v>104</v>
-      </c>
-      <c r="C969" t="s">
-        <v>105</v>
-      </c>
-      <c r="D969" t="s">
-        <v>104</v>
-      </c>
-      <c r="E969" t="s">
-        <v>374</v>
-      </c>
-      <c r="F969" t="s">
-        <v>24</v>
-      </c>
-      <c r="G969" t="s">
-        <v>375</v>
-      </c>
-      <c r="H969" t="s">
-        <v>376</v>
-      </c>
-      <c r="I969" t="s">
-        <v>24</v>
-      </c>
-      <c r="J969">
-        <v>30</v>
-      </c>
-      <c r="K969">
-        <v>0</v>
-      </c>
-      <c r="L969" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="970" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A970">
-        <v>4604</v>
-      </c>
-      <c r="B970" t="s">
-        <v>110</v>
-      </c>
-      <c r="C970" t="s">
-        <v>111</v>
-      </c>
-      <c r="D970" t="s">
-        <v>110</v>
-      </c>
-      <c r="E970" t="s">
-        <v>374</v>
-      </c>
-      <c r="F970" t="s">
-        <v>24</v>
-      </c>
-      <c r="G970" t="s">
-        <v>375</v>
-      </c>
-      <c r="H970" t="s">
-        <v>376</v>
-      </c>
-      <c r="I970" t="s">
-        <v>24</v>
-      </c>
-      <c r="J970">
-        <v>6</v>
-      </c>
-      <c r="K970">
-        <v>0</v>
-      </c>
-      <c r="L970" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="971" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A971">
-        <v>4604</v>
-      </c>
-      <c r="B971" t="s">
-        <v>124</v>
-      </c>
-      <c r="C971" t="s">
-        <v>125</v>
-      </c>
-      <c r="D971" t="s">
-        <v>124</v>
-      </c>
-      <c r="E971" t="s">
-        <v>374</v>
-      </c>
-      <c r="F971" t="s">
-        <v>24</v>
-      </c>
-      <c r="G971" t="s">
-        <v>375</v>
-      </c>
-      <c r="H971" t="s">
-        <v>376</v>
-      </c>
-      <c r="I971" t="s">
-        <v>24</v>
-      </c>
-      <c r="J971">
-        <v>6</v>
-      </c>
-      <c r="K971">
-        <v>0</v>
-      </c>
-      <c r="L971" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="972" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A972">
-        <v>4604</v>
-      </c>
-      <c r="B972" t="s">
-        <v>134</v>
-      </c>
-      <c r="C972" t="s">
-        <v>135</v>
-      </c>
-      <c r="D972" t="s">
-        <v>134</v>
-      </c>
-      <c r="E972" t="s">
-        <v>374</v>
-      </c>
-      <c r="F972" t="s">
-        <v>24</v>
-      </c>
-      <c r="G972" t="s">
-        <v>375</v>
-      </c>
-      <c r="H972" t="s">
-        <v>376</v>
-      </c>
-      <c r="I972" t="s">
-        <v>24</v>
-      </c>
-      <c r="J972">
-        <v>6</v>
-      </c>
-      <c r="K972">
-        <v>0</v>
-      </c>
-      <c r="L972" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="973" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A973">
-        <v>4604</v>
-      </c>
-      <c r="B973" t="s">
-        <v>144</v>
-      </c>
-      <c r="C973" t="s">
-        <v>145</v>
-      </c>
-      <c r="D973" t="s">
-        <v>144</v>
-      </c>
-      <c r="E973" t="s">
-        <v>374</v>
-      </c>
-      <c r="F973" t="s">
-        <v>24</v>
-      </c>
-      <c r="G973" t="s">
-        <v>375</v>
-      </c>
-      <c r="H973" t="s">
-        <v>376</v>
-      </c>
-      <c r="I973" t="s">
-        <v>24</v>
-      </c>
-      <c r="J973">
-        <v>18</v>
-      </c>
-      <c r="K973">
-        <v>0</v>
-      </c>
-      <c r="L973" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="974" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A974">
-        <v>4604</v>
-      </c>
-      <c r="B974" t="s">
-        <v>150</v>
-      </c>
-      <c r="C974" t="s">
-        <v>151</v>
-      </c>
-      <c r="D974" t="s">
-        <v>150</v>
-      </c>
-      <c r="E974" t="s">
-        <v>374</v>
-      </c>
-      <c r="F974" t="s">
-        <v>24</v>
-      </c>
-      <c r="G974" t="s">
-        <v>375</v>
-      </c>
-      <c r="H974" t="s">
-        <v>376</v>
-      </c>
-      <c r="I974" t="s">
-        <v>24</v>
-      </c>
-      <c r="J974">
-        <v>36</v>
-      </c>
-      <c r="K974">
-        <v>0</v>
-      </c>
-      <c r="L974" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="975" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A975">
-        <v>4604</v>
-      </c>
-      <c r="B975" t="s">
-        <v>270</v>
-      </c>
-      <c r="C975" t="s">
-        <v>271</v>
-      </c>
-      <c r="D975" t="s">
-        <v>270</v>
-      </c>
-      <c r="E975" t="s">
-        <v>374</v>
-      </c>
-      <c r="F975" t="s">
-        <v>24</v>
-      </c>
-      <c r="G975" t="s">
-        <v>375</v>
-      </c>
-      <c r="H975" t="s">
-        <v>376</v>
-      </c>
-      <c r="I975" t="s">
-        <v>24</v>
-      </c>
-      <c r="J975">
-        <v>12</v>
-      </c>
-      <c r="K975">
-        <v>0</v>
-      </c>
-      <c r="L975" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="976" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A976">
-        <v>4604</v>
-      </c>
-      <c r="B976" t="s">
-        <v>554</v>
-      </c>
-      <c r="C976" t="s">
-        <v>555</v>
-      </c>
-      <c r="D976" t="s">
-        <v>554</v>
-      </c>
-      <c r="E976" t="s">
-        <v>374</v>
-      </c>
-      <c r="F976" t="s">
-        <v>24</v>
-      </c>
-      <c r="G976" t="s">
-        <v>375</v>
-      </c>
-      <c r="H976" t="s">
-        <v>376</v>
-      </c>
-      <c r="I976" t="s">
-        <v>24</v>
-      </c>
-      <c r="J976">
-        <v>12</v>
-      </c>
-      <c r="K976">
-        <v>0</v>
-      </c>
-      <c r="L976" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="977" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A977">
-        <v>4604</v>
-      </c>
-      <c r="B977" t="s">
-        <v>162</v>
-      </c>
-      <c r="C977" t="s">
-        <v>163</v>
-      </c>
-      <c r="D977" t="s">
-        <v>162</v>
-      </c>
-      <c r="E977" t="s">
-        <v>374</v>
-      </c>
-      <c r="F977" t="s">
-        <v>24</v>
-      </c>
-      <c r="G977" t="s">
-        <v>375</v>
-      </c>
-      <c r="H977" t="s">
-        <v>376</v>
-      </c>
-      <c r="I977" t="s">
-        <v>24</v>
-      </c>
-      <c r="J977">
-        <v>6</v>
-      </c>
-      <c r="K977">
-        <v>0</v>
-      </c>
-      <c r="L977" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="978" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A978">
-        <v>4604</v>
-      </c>
-      <c r="B978" t="s">
-        <v>172</v>
-      </c>
-      <c r="C978" t="s">
-        <v>173</v>
-      </c>
-      <c r="D978" t="s">
-        <v>172</v>
-      </c>
-      <c r="E978" t="s">
-        <v>374</v>
-      </c>
-      <c r="F978" t="s">
-        <v>24</v>
-      </c>
-      <c r="G978" t="s">
-        <v>375</v>
-      </c>
-      <c r="H978" t="s">
-        <v>376</v>
-      </c>
-      <c r="I978" t="s">
-        <v>24</v>
-      </c>
-      <c r="J978">
-        <v>12</v>
-      </c>
-      <c r="K978">
-        <v>0</v>
-      </c>
-      <c r="L978" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="979" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A979">
-        <v>4604</v>
-      </c>
-      <c r="B979" t="s">
-        <v>634</v>
-      </c>
-      <c r="C979" t="s">
-        <v>635</v>
-      </c>
-      <c r="D979" t="s">
-        <v>634</v>
-      </c>
-      <c r="E979" t="s">
-        <v>374</v>
-      </c>
-      <c r="F979" t="s">
-        <v>24</v>
-      </c>
-      <c r="G979" t="s">
-        <v>375</v>
-      </c>
-      <c r="H979" t="s">
-        <v>376</v>
-      </c>
-      <c r="I979" t="s">
-        <v>24</v>
-      </c>
-      <c r="J979">
-        <v>6</v>
-      </c>
-      <c r="K979">
-        <v>0</v>
-      </c>
-      <c r="L979" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="980" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A980">
-        <v>4604</v>
-      </c>
-      <c r="B980" t="s">
-        <v>206</v>
-      </c>
-      <c r="C980" t="s">
-        <v>207</v>
-      </c>
-      <c r="D980" t="s">
-        <v>206</v>
-      </c>
-      <c r="E980" t="s">
-        <v>374</v>
-      </c>
-      <c r="F980" t="s">
-        <v>24</v>
-      </c>
-      <c r="G980" t="s">
-        <v>375</v>
-      </c>
-      <c r="H980" t="s">
-        <v>376</v>
-      </c>
-      <c r="I980" t="s">
-        <v>24</v>
-      </c>
-      <c r="J980">
-        <v>18</v>
-      </c>
-      <c r="K980">
-        <v>0</v>
-      </c>
-      <c r="L980" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="981" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A981">
-        <v>4604</v>
-      </c>
-      <c r="B981" t="s">
-        <v>208</v>
-      </c>
-      <c r="C981" t="s">
-        <v>209</v>
-      </c>
-      <c r="D981" t="s">
-        <v>208</v>
-      </c>
-      <c r="E981" t="s">
-        <v>374</v>
-      </c>
-      <c r="F981" t="s">
-        <v>24</v>
-      </c>
-      <c r="G981" t="s">
-        <v>375</v>
-      </c>
-      <c r="H981" t="s">
-        <v>376</v>
-      </c>
-      <c r="I981" t="s">
-        <v>24</v>
-      </c>
-      <c r="J981">
-        <v>3</v>
-      </c>
-      <c r="K981">
-        <v>0</v>
-      </c>
-      <c r="L981" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="982" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A982">
-        <v>4604</v>
-      </c>
-      <c r="B982" t="s">
-        <v>210</v>
-      </c>
-      <c r="C982" t="s">
-        <v>211</v>
-      </c>
-      <c r="D982" t="s">
-        <v>210</v>
-      </c>
-      <c r="E982" t="s">
-        <v>374</v>
-      </c>
-      <c r="F982" t="s">
-        <v>24</v>
-      </c>
-      <c r="G982" t="s">
-        <v>375</v>
-      </c>
-      <c r="H982" t="s">
-        <v>376</v>
-      </c>
-      <c r="I982" t="s">
-        <v>24</v>
-      </c>
-      <c r="J982">
-        <v>3</v>
-      </c>
-      <c r="K982">
-        <v>0</v>
-      </c>
-      <c r="L982" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="983" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A983">
-        <v>4604</v>
-      </c>
-      <c r="B983" t="s">
-        <v>220</v>
-      </c>
-      <c r="C983" t="s">
-        <v>221</v>
-      </c>
-      <c r="D983" t="s">
-        <v>220</v>
-      </c>
-      <c r="E983" t="s">
-        <v>374</v>
-      </c>
-      <c r="F983" t="s">
-        <v>24</v>
-      </c>
-      <c r="G983" t="s">
-        <v>375</v>
-      </c>
-      <c r="H983" t="s">
-        <v>376</v>
-      </c>
-      <c r="I983" t="s">
-        <v>24</v>
-      </c>
-      <c r="J983">
-        <v>12</v>
-      </c>
-      <c r="K983">
-        <v>0</v>
-      </c>
-      <c r="L983" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="984" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A984">
-        <v>4604</v>
-      </c>
-      <c r="B984" t="s">
-        <v>707</v>
-      </c>
-      <c r="C984" t="s">
-        <v>708</v>
-      </c>
-      <c r="D984" t="s">
-        <v>707</v>
-      </c>
-      <c r="E984" t="s">
-        <v>374</v>
-      </c>
-      <c r="F984" t="s">
-        <v>24</v>
-      </c>
-      <c r="G984" t="s">
-        <v>375</v>
-      </c>
-      <c r="H984" t="s">
-        <v>376</v>
-      </c>
-      <c r="I984" t="s">
-        <v>24</v>
-      </c>
-      <c r="J984">
-        <v>3</v>
-      </c>
-      <c r="K984">
-        <v>0</v>
-      </c>
-      <c r="L984" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="985" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A985">
-        <v>4604</v>
-      </c>
-      <c r="B985" t="s">
-        <v>697</v>
-      </c>
-      <c r="C985" t="s">
-        <v>698</v>
-      </c>
-      <c r="D985" t="s">
-        <v>697</v>
-      </c>
-      <c r="E985" t="s">
-        <v>374</v>
-      </c>
-      <c r="F985" t="s">
-        <v>24</v>
-      </c>
-      <c r="G985" t="s">
-        <v>375</v>
-      </c>
-      <c r="H985" t="s">
-        <v>376</v>
-      </c>
-      <c r="I985" t="s">
-        <v>24</v>
-      </c>
-      <c r="J985">
-        <v>3</v>
-      </c>
-      <c r="K985">
-        <v>0</v>
-      </c>
-      <c r="L985" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="986" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A986">
-        <v>4604</v>
-      </c>
-      <c r="B986" t="s">
-        <v>709</v>
-      </c>
-      <c r="C986" t="s">
-        <v>710</v>
-      </c>
-      <c r="D986" t="s">
-        <v>709</v>
-      </c>
-      <c r="E986" t="s">
-        <v>374</v>
-      </c>
-      <c r="F986" t="s">
-        <v>24</v>
-      </c>
-      <c r="G986" t="s">
-        <v>375</v>
-      </c>
-      <c r="H986" t="s">
-        <v>376</v>
-      </c>
-      <c r="I986" t="s">
-        <v>24</v>
-      </c>
-      <c r="J986">
-        <v>3</v>
-      </c>
-      <c r="K986">
-        <v>0</v>
-      </c>
-      <c r="L986" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="987" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A987">
-        <v>4604</v>
-      </c>
-      <c r="B987" t="s">
-        <v>292</v>
-      </c>
-      <c r="C987" t="s">
-        <v>293</v>
-      </c>
-      <c r="D987" t="s">
-        <v>292</v>
-      </c>
-      <c r="E987" t="s">
-        <v>374</v>
-      </c>
-      <c r="F987" t="s">
-        <v>24</v>
-      </c>
-      <c r="G987" t="s">
-        <v>375</v>
-      </c>
-      <c r="H987" t="s">
-        <v>376</v>
-      </c>
-      <c r="I987" t="s">
-        <v>24</v>
-      </c>
-      <c r="J987">
-        <v>3</v>
-      </c>
-      <c r="K987">
-        <v>0</v>
-      </c>
-      <c r="L987" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="988" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A988">
-        <v>4604</v>
-      </c>
-      <c r="B988" t="s">
-        <v>244</v>
-      </c>
-      <c r="C988" t="s">
-        <v>245</v>
-      </c>
-      <c r="D988" t="s">
-        <v>244</v>
-      </c>
-      <c r="E988" t="s">
-        <v>374</v>
-      </c>
-      <c r="F988" t="s">
-        <v>24</v>
-      </c>
-      <c r="G988" t="s">
-        <v>375</v>
-      </c>
-      <c r="H988" t="s">
-        <v>376</v>
-      </c>
-      <c r="I988" t="s">
-        <v>24</v>
-      </c>
-      <c r="J988">
-        <v>6</v>
-      </c>
-      <c r="K988">
-        <v>0</v>
-      </c>
-      <c r="L988" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="989" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A989">
-        <v>4604</v>
-      </c>
-      <c r="B989" t="s">
-        <v>266</v>
-      </c>
-      <c r="C989" t="s">
-        <v>267</v>
-      </c>
-      <c r="D989" t="s">
-        <v>266</v>
-      </c>
-      <c r="E989" t="s">
-        <v>374</v>
-      </c>
-      <c r="F989" t="s">
-        <v>24</v>
-      </c>
-      <c r="G989" t="s">
-        <v>375</v>
-      </c>
-      <c r="H989" t="s">
-        <v>376</v>
-      </c>
-      <c r="I989" t="s">
-        <v>24</v>
-      </c>
-      <c r="J989">
-        <v>6</v>
-      </c>
-      <c r="K989">
-        <v>0</v>
-      </c>
-      <c r="L989" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="990" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A990">
-        <v>4605</v>
-      </c>
-      <c r="B990" t="s">
-        <v>102</v>
-      </c>
-      <c r="C990" t="s">
-        <v>103</v>
-      </c>
-      <c r="D990" t="s">
-        <v>102</v>
-      </c>
-      <c r="E990" t="s">
-        <v>374</v>
-      </c>
-      <c r="F990" t="s">
-        <v>24</v>
-      </c>
-      <c r="G990" t="s">
-        <v>375</v>
-      </c>
-      <c r="H990" t="s">
-        <v>376</v>
-      </c>
-      <c r="I990" t="s">
-        <v>24</v>
-      </c>
-      <c r="J990">
-        <v>3630</v>
-      </c>
-      <c r="K990">
-        <v>0</v>
-      </c>
-      <c r="L990" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="991" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A991">
-        <v>4605</v>
-      </c>
-      <c r="B991" t="s">
-        <v>104</v>
-      </c>
-      <c r="C991" t="s">
-        <v>105</v>
-      </c>
-      <c r="D991" t="s">
-        <v>104</v>
-      </c>
-      <c r="E991" t="s">
-        <v>374</v>
-      </c>
-      <c r="F991" t="s">
-        <v>24</v>
-      </c>
-      <c r="G991" t="s">
-        <v>375</v>
-      </c>
-      <c r="H991" t="s">
-        <v>376</v>
-      </c>
-      <c r="I991" t="s">
-        <v>24</v>
-      </c>
-      <c r="J991">
-        <v>3612</v>
-      </c>
-      <c r="K991">
-        <v>0</v>
-      </c>
-      <c r="L991" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="992" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A992">
-        <v>4606</v>
-      </c>
-      <c r="B992" t="s">
-        <v>422</v>
-      </c>
-      <c r="C992" t="s">
-        <v>423</v>
-      </c>
-      <c r="D992" t="s">
-        <v>422</v>
-      </c>
-      <c r="E992" t="s">
-        <v>374</v>
-      </c>
-      <c r="F992" t="s">
-        <v>24</v>
-      </c>
-      <c r="G992" t="s">
-        <v>375</v>
-      </c>
-      <c r="H992" t="s">
-        <v>376</v>
-      </c>
-      <c r="I992" t="s">
-        <v>24</v>
-      </c>
-      <c r="J992">
-        <v>2</v>
-      </c>
-      <c r="K992">
-        <v>17</v>
-      </c>
-      <c r="L992" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="993" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A993">
-        <v>4606</v>
-      </c>
-      <c r="B993" t="s">
-        <v>428</v>
-      </c>
-      <c r="C993" t="s">
-        <v>429</v>
-      </c>
-      <c r="D993" t="s">
-        <v>428</v>
-      </c>
-      <c r="E993" t="s">
-        <v>374</v>
-      </c>
-      <c r="F993" t="s">
-        <v>24</v>
-      </c>
-      <c r="G993" t="s">
-        <v>375</v>
-      </c>
-      <c r="H993" t="s">
-        <v>376</v>
-      </c>
-      <c r="I993" t="s">
-        <v>24</v>
-      </c>
-      <c r="J993">
-        <v>2</v>
-      </c>
-      <c r="K993">
-        <v>28</v>
-      </c>
-      <c r="L993" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="994" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A994">
-        <v>4607</v>
-      </c>
-      <c r="B994" t="s">
-        <v>422</v>
-      </c>
-      <c r="C994" t="s">
-        <v>423</v>
-      </c>
-      <c r="D994" t="s">
-        <v>422</v>
-      </c>
-      <c r="E994" t="s">
-        <v>374</v>
-      </c>
-      <c r="F994" t="s">
-        <v>24</v>
-      </c>
-      <c r="G994" t="s">
-        <v>375</v>
-      </c>
-      <c r="H994" t="s">
-        <v>376</v>
-      </c>
-      <c r="I994" t="s">
-        <v>24</v>
-      </c>
-      <c r="J994">
-        <v>3</v>
-      </c>
-      <c r="K994">
-        <v>26</v>
-      </c>
-      <c r="L994" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="995" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A995">
-        <v>4607</v>
-      </c>
-      <c r="B995" t="s">
-        <v>428</v>
-      </c>
-      <c r="C995" t="s">
-        <v>429</v>
-      </c>
-      <c r="D995" t="s">
-        <v>428</v>
-      </c>
-      <c r="E995" t="s">
-        <v>374</v>
-      </c>
-      <c r="F995" t="s">
-        <v>24</v>
-      </c>
-      <c r="G995" t="s">
-        <v>375</v>
-      </c>
-      <c r="H995" t="s">
-        <v>376</v>
-      </c>
-      <c r="I995" t="s">
-        <v>24</v>
-      </c>
-      <c r="J995">
-        <v>1</v>
-      </c>
-      <c r="K995">
-        <v>50</v>
-      </c>
-      <c r="L995" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="996" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A996">
-        <v>4608</v>
-      </c>
-      <c r="B996" t="s">
-        <v>422</v>
-      </c>
-      <c r="C996" t="s">
-        <v>423</v>
-      </c>
-      <c r="D996" t="s">
-        <v>422</v>
-      </c>
-      <c r="E996" t="s">
-        <v>374</v>
-      </c>
-      <c r="F996" t="s">
-        <v>24</v>
-      </c>
-      <c r="G996" t="s">
-        <v>375</v>
-      </c>
-      <c r="H996" t="s">
-        <v>376</v>
-      </c>
-      <c r="I996" t="s">
-        <v>24</v>
-      </c>
-      <c r="J996">
-        <v>3</v>
-      </c>
-      <c r="K996">
-        <v>6</v>
-      </c>
-      <c r="L996" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="997" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A997">
-        <v>4608</v>
-      </c>
-      <c r="B997" t="s">
-        <v>428</v>
-      </c>
-      <c r="C997" t="s">
-        <v>429</v>
-      </c>
-      <c r="D997" t="s">
-        <v>428</v>
-      </c>
-      <c r="E997" t="s">
-        <v>374</v>
-      </c>
-      <c r="F997" t="s">
-        <v>24</v>
-      </c>
-      <c r="G997" t="s">
-        <v>375</v>
-      </c>
-      <c r="H997" t="s">
-        <v>376</v>
-      </c>
-      <c r="I997" t="s">
-        <v>24</v>
-      </c>
-      <c r="J997">
-        <v>2</v>
-      </c>
-      <c r="K997">
-        <v>0</v>
-      </c>
-      <c r="L997" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="998" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A998">
-        <v>4609</v>
-      </c>
-      <c r="B998" t="s">
-        <v>422</v>
-      </c>
-      <c r="C998" t="s">
-        <v>423</v>
-      </c>
-      <c r="D998" t="s">
-        <v>422</v>
-      </c>
-      <c r="E998" t="s">
-        <v>374</v>
-      </c>
-      <c r="F998" t="s">
-        <v>24</v>
-      </c>
-      <c r="G998" t="s">
-        <v>375</v>
-      </c>
-      <c r="H998" t="s">
-        <v>376</v>
-      </c>
-      <c r="I998" t="s">
-        <v>24</v>
-      </c>
-      <c r="J998">
-        <v>2</v>
-      </c>
-      <c r="K998">
-        <v>29</v>
-      </c>
-      <c r="L998" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="999" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A999">
-        <v>4609</v>
-      </c>
-      <c r="B999" t="s">
-        <v>428</v>
-      </c>
-      <c r="C999" t="s">
-        <v>429</v>
-      </c>
-      <c r="D999" t="s">
-        <v>428</v>
-      </c>
-      <c r="E999" t="s">
-        <v>374</v>
-      </c>
-      <c r="F999" t="s">
-        <v>24</v>
-      </c>
-      <c r="G999" t="s">
-        <v>375</v>
-      </c>
-      <c r="H999" t="s">
-        <v>376</v>
-      </c>
-      <c r="I999" t="s">
-        <v>24</v>
-      </c>
-      <c r="J999">
-        <v>2</v>
-      </c>
-      <c r="K999">
-        <v>25</v>
-      </c>
-      <c r="L999" t="s">
-        <v>427</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
